--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>** 전북대, BAE시스템즈코리아와 '방산 인재 양성' 협약</t>
+          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014036617?sid=102</t>
+          <t>https://sjbnews.com/news/news.php?number=887083</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 11:31:00 +0900</t>
+          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/06/30/NISI20260630_0002173709_web_20260630112722_20260630113224963.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/06/30/NISI20260630_0002173709_web_20260630112722_20260630113224963.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>** 전북대-비에이이 시스템스 코리아, 방위산업·첨단기술 인재양성·산학...</t>
+          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003442667?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 11:09:00 +0900</t>
+          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/06/30/0003442667_001_20260630194557718.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/06/30/0003442667_001_20260630194557718.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -942,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
+          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -966,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
+          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -990,23 +990,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
+          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
+        </is>
+      </c>
+      <c r="E24">
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1015,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
+          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
+          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
+          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1039,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
+          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
+          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1063,22 +1062,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
+          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E27">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1087,21 +1087,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
+          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
+          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1111,21 +1111,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
+          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
+          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
+          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1135,21 +1135,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
+          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
+          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1159,21 +1159,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
+          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
+          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1183,21 +1183,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
+          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
+          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
+          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
+        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1207,21 +1207,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
+          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://hbnpress.com/news/view/1065597442480538</t>
+          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
+          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
+          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
+          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1255,21 +1255,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
+          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
         <v/>
       </c>
     </row>
@@ -1279,21 +1279,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
+          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
+          <t>https://hbnpress.com/news/view/1065597442480538</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
+        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1303,21 +1303,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
+          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
+          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1327,21 +1327,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
+          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
+          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1351,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
+          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
+          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
+        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1375,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
+          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
+          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
+          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
+          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
+          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
+          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
+          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
+          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
         <v/>
       </c>
     </row>
@@ -1495,21 +1495,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
+          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
+          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
+          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
         <v/>
       </c>
     </row>
@@ -1543,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
+          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
+          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1567,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
+          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
+          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1615,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
+          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260819500013</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
+          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260907022502", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260907022502"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1639,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
+          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
+          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1663,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
+          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260817500461</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
+          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260907022516", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260907022516"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1687,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
+          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
+          <t>https://www.viva100.com/article/20260819500013</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260908035556", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260908035556"))</f>
         <v/>
       </c>
     </row>
@@ -1711,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
+          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1735,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>전북대학교, 세계 명문대·글로벌 기업 손잡고 '글로벌 산학연 허브' 도...</t>
+          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208484</t>
+          <t>https://www.viva100.com/article/20260817500461</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 20:30:00 +0900</t>
+          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208484_477348_3537_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208484_477348_3537_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260908035613", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260908035613"))</f>
         <v/>
       </c>
     </row>
@@ -1759,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>전북대, 전국 AI 자율주행 경진대회 석권</t>
+          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/056/0012236878?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Thu, 13 Aug 2026 08:47:00 +0900</t>
+          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/056/2026/08/13/0012236878_001_20260813085643884.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/056/2026/08/13/0012236878_001_20260813085643884.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
+          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260812500685</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
+          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260907022528", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260907022528"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1807,21 +1807,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
+          <t>전북대학교, 세계 명문대·글로벌 기업 손잡고 '글로벌 산학연 허브' 도...</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208484</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
+          <t>Fri, 14 Aug 2026 20:30:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208484_477348_3537_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208484_477348_3537_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1831,21 +1831,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
+          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
+          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
+          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1855,21 +1855,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1879,21 +1879,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1903,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
+          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
+          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1927,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
+          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
+          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1951,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
+          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
+          <t>https://www.ajunews.com/view/20260806162915186</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
+          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1975,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
+          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
+          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
+          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260806162915186</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2023,21 +2023,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
+          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
+          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
+          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2047,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
+          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
+          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2095,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
+          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
+          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2143,21 +2143,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
+          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
+          <t>https://www.betanews.net/article/view/beta202607290020</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
+          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2167,21 +2167,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
+          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
+          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2191,21 +2191,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
+          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607290020</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2215,21 +2215,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
+          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2239,21 +2239,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
+          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
+          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2263,21 +2263,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
+          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
+          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2287,21 +2287,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
+          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
+          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2311,21 +2311,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
+          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
+          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2335,21 +2335,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
+          <t>고려대-전북대 국가균형발전 이끄는 산/학/연 협력 허브 구축 협약</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621016</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
+          <t>Mon, 27 Jul 2026 13:50:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621016_534040_4114_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621016_534040_4114_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2359,21 +2359,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
+          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
+          <t>https://www.viva100.com/article/20260726500503</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
+          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260908035737", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260908035737"))</f>
         <v/>
       </c>
     </row>
@@ -2383,21 +2383,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>고려대-전북대 국가균형발전 이끄는 산/학/연 협력 허브 구축 협약</t>
+          <t>오성훈 전북대 교수, 강호항공고서 진로 특강</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621016</t>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1562918</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 13:50:00 +0900</t>
+          <t>Fri, 24 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621016_534040_4114_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621016_534040_4114_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202607/1562918_774586_3414_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202607/1562918_774586_3414_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2407,21 +2407,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
+          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260726500503</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
+          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260907022658", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260907022658"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2431,21 +2431,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>오성훈 전북대 교수, 강호항공고서 진로 특강</t>
+          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1562918</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 15:42:00 +0900</t>
+          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202607/1562918_774586_3414_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202607/1562918_774586_3414_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2455,21 +2455,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
+          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
+          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2479,21 +2479,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
+          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
+          <t>https://www.viva100.com/article/20260812500685</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
+          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260908035750", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260908035750"))</f>
         <v/>
       </c>
     </row>
@@ -2503,21 +2503,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
+          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2527,21 +2527,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
+          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2551,21 +2551,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
+          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
+          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
         <v/>
       </c>
     </row>
@@ -2575,21 +2575,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
+          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
+          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2599,21 +2599,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
+          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
+          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2623,21 +2623,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
+          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
+          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2647,21 +2647,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
+          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2671,21 +2671,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
+          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2695,21 +2695,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
+          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
+          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2719,21 +2719,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
+          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
+          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2743,21 +2743,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
+          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
+          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
         <v/>
       </c>
     </row>
@@ -2767,21 +2767,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
+          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
+          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2791,21 +2791,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
+          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
+          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2815,21 +2815,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
+          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2605457</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
+          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2839,21 +2839,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
+          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
+          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2863,21 +2863,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
+          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
+          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
+          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2887,21 +2887,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
+          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
+          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2911,21 +2911,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
+          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
+          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2935,21 +2935,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
+          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
+          <t>https://www.ajunews.com/view/20260714135200349</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
+          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
         <v/>
       </c>
     </row>
@@ -2959,21 +2959,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
+          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
+          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
+          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
+        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2983,21 +2983,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
+          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260714135200349</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
+          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3007,21 +3007,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
+          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
+          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
+          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3031,21 +3031,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
+          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
+          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3055,21 +3055,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
+          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
+          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3079,21 +3079,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
+          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
+          <t>https://www.viva100.com/article/20260712500414</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
+          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260908035901", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260908035901"))</f>
         <v/>
       </c>
     </row>
@@ -3103,21 +3103,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
+          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
+          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3127,21 +3127,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
+          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260712500414</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
+          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260907022835", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260907022835"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3151,21 +3151,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
+          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
+          <t>https://www.news2day.co.kr/article/20260709500128</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
+          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
         <v/>
       </c>
     </row>
@@ -3175,21 +3175,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
+          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
+          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
+          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3199,21 +3199,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
+          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260709500128</t>
+          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3223,21 +3223,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
+          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3247,21 +3247,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
+          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
+          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3271,21 +3271,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
+          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3295,21 +3295,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
+          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3319,21 +3319,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
+          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
+          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
+          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3367,21 +3367,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
+          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
+          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3391,21 +3391,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
+          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
+          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
+          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3415,21 +3415,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
+          <t>&amp;quot;방산 기술·MRO 합친 '패키지 수출' 늘려야&amp;quot;</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005304632?sid=101</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
+          <t>Tue, 30 Jun 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3439,21 +3439,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3463,21 +3463,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>&amp;quot;방산 기술·MRO 합친 '패키지 수출' 늘려야&amp;quot;</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005304632?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 17:32:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4172,10 +4172,9 @@
           <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+      <c r="E156">
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -4520,21 +4519,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
+          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
+          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
+          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
         </is>
       </c>
       <c r="E171">
-        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4544,21 +4543,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
+          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
+          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E172">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4568,21 +4567,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
+          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
+          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E173">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4592,21 +4591,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
+          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
         </is>
       </c>
       <c r="E174">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4616,21 +4615,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
+          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
+          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
         </is>
       </c>
       <c r="E175">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4640,21 +4639,21 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
+          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
+          <t>https://www.etoday.co.kr/news/view/2605457</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
+          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
         </is>
       </c>
       <c r="E176">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
         <v/>
       </c>
     </row>
@@ -4664,21 +4663,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
+          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
+          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E177">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4688,21 +4687,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
+          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
+          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
         </is>
       </c>
       <c r="E178">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4712,21 +4711,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
+          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
+          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
         </is>
       </c>
       <c r="E179">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4736,21 +4735,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>성능보다 우선한 '동맹'…캐나다, 왜 독일 선택했나?</t>
+          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000625036?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 21:20:00 +0900</t>
+          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E180">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4760,21 +4759,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>나토 국방비 증액에도 생산 병목…기회 잡는 K-방산</t>
+          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>http://www.metroseoul.co.kr/article/20260707500477</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:54:00 +0900</t>
+          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E181">
-        <f>HYPERLINK("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg", IMAGE("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4784,21 +4783,21 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>K-방산, 캐나다서 아쉬운 고배…나토 시장 공략 숙제 남겼다</t>
+          <t>성능보다 우선한 '동맹'…캐나다, 왜 독일 선택했나?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260707010002482</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000625036?sid=101</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 14:30:00 +0900</t>
+          <t>Tue, 07 Jul 2026 21:20:00 +0900</t>
         </is>
       </c>
       <c r="E182">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/08d/2026070701000473600024821.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/08d/2026070701000473600024821.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4808,23 +4807,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>120조 캐나다 잠수함 ‘운명의 한 주’…한화오션, 새 역사 쓸까</t>
+          <t>나토 국방비 증액에도 생산 병목…기회 잡는 K-방산</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1306065&amp;inflow=N</t>
+          <t>http://www.metroseoul.co.kr/article/20260707500477</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Fri, 03 Jul 2026 12:14:00 +0900</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 07 Jul 2026 16:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E183">
+        <f>HYPERLINK("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg", IMAGE("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="184">
@@ -4833,23 +4831,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>한화오션 차기 구축함 수주 되레 '독배' 되나, 원가 상승에 수익성 해법...</t>
+          <t>K-방산, 캐나다서 아쉬운 고배…나토 시장 공략 숙제 남겼다</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=441425</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260707010002482</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Thu, 02 Jul 2026 16:56:00 +0900</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 07 Jul 2026 14:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E184">
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/08d/2026070701000473600024821.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/08d/2026070701000473600024821.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="185">
@@ -4971,21 +4968,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>** [뉴스1전북포럼]장원준 교수 &amp;quot;전북 방위산업 성공 조건은 첨단소재 플랫...</t>
+          <t>** 황인홍 무주군수, 전북포럼서 방위산업 육성 전략 발제</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009077035?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004171759?sid=102</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 12:08:00 +0900</t>
+          <t>Fri, 24 Jul 2026 13:39:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/24/0009077035_001_20260724124415958.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/24/0009077035_001_20260724124415958.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4995,21 +4992,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>** 황인홍 무주군수, 전북포럼서 방위산업 육성 전략 발제</t>
+          <t>** [뉴스1전북포럼]장원준 교수 &amp;quot;전북 방위산업 성공 조건은 첨단소재 플랫...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004171759?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009077035?sid=102</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 13:39:00 +0900</t>
+          <t>Fri, 24 Jul 2026 12:08:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/24/0009077035_001_20260724124415958.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/24/0009077035_001_20260724124415958.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5043,21 +5040,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>** 포티투마루, ‘글로벌 디지털 포럼’에서 K-팔란티어 육성 전략 제시</t>
+          <t>** [2026방산포럼] '한·UAE' 방산 협력 넓힌다···AI부터 KF-21까지 협력...</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2605499</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2444556</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 21 Jul 2026 09:18:00 +0900</t>
+          <t>Thu, 02 Jul 2026 03:51:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2444556_1281841_516_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2444556_1281841_516_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -5067,21 +5064,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>** [2026방산포럼] '한·UAE' 방산 협력 넓힌다···AI부터 KF-21까지 협력...</t>
+          <t>** K방산 수출, 이제는 정보다 [기고]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2444556</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 02 Jul 2026 03:51:00 +0900</t>
+          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2444556_1281841_516_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2444556_1281841_516_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5091,21 +5088,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>** K방산 수출, 이제는 정보다 [기고]</t>
+          <t>** 포티투마루, ‘글로벌 디지털 포럼’에서 K-팔란티어 육성 전략 제시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
+          <t>https://www.etoday.co.kr/news/view/2605499</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
+          <t>Tue, 21 Jul 2026 09:18:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>** 전북대-글로벌 방산기업 BAE Systems Korea '전략적 협력 MOU' 체결.. '방...</t>
+          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=617196</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 13:06:00 +0900</t>
+          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202606/617196_530269_5210_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202606/617196_530269_5210_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260908035556", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260908035556"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260909031119", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260909031119"))</f>
         <v/>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260908035613", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260908035613"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260909031130", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260909031130"))</f>
         <v/>
       </c>
     </row>
@@ -1831,21 +1831,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
+          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
+          <t>https://www.ajunews.com/view/20260908164442351</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
+          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1855,21 +1855,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
+          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
+          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
+          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1879,21 +1879,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
+          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
+          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1903,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
+          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
+          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1927,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
+          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
+          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1951,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
+          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260806162915186</t>
+          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
+          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1975,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
+          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
+          <t>https://www.ajunews.com/view/20260806162915186</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
+          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
+          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
+          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
+          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2023,21 +2023,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
+          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2047,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
+          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
+          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
+          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
+        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
+          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2095,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
+          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
+          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -2143,21 +2143,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
+          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607290020</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2167,21 +2167,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
+          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
+          <t>https://www.betanews.net/article/view/beta202607290020</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2191,21 +2191,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
+          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
+          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2215,21 +2215,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
+          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2239,21 +2239,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
+          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
+          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2263,21 +2263,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
+          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
+          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2287,21 +2287,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
+          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
+          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2311,21 +2311,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
+          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
+          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2335,21 +2335,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>고려대-전북대 국가균형발전 이끄는 산/학/연 협력 허브 구축 협약</t>
+          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621016</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 13:50:00 +0900</t>
+          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621016_534040_4114_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621016_534040_4114_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2359,21 +2359,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
+          <t>고려대-전북대 국가균형발전 이끄는 산/학/연 협력 허브 구축 협약</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260726500503</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621016</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
+          <t>Mon, 27 Jul 2026 13:50:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260908035737", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260908035737"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621016_534040_4114_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621016_534040_4114_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2383,21 +2383,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>오성훈 전북대 교수, 강호항공고서 진로 특강</t>
+          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1562918</t>
+          <t>https://www.viva100.com/article/20260726500503</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 15:42:00 +0900</t>
+          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202607/1562918_774586_3414_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202607/1562918_774586_3414_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260909031244", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260909031244"))</f>
         <v/>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260908035750", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260908035750"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260909031252", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260909031252"))</f>
         <v/>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260908035901", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260908035901"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260909031353", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260909031353"))</f>
         <v/>
       </c>
     </row>
@@ -3116,9 +3116,10 @@
           <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
         </is>
       </c>
-      <c r="E112">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
-        <v/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -4172,9 +4173,10 @@
           <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
-      <c r="E156">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
-        <v/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -4944,21 +4946,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>** [뉴스1전북포럼] &amp;quot;전북 방산 육성, 인재·시험평가·실증 기반 갖춰야&amp;quot;(...</t>
+          <t>** 황인홍 무주군수, 전북포럼서 방위산업 육성 전략 발제</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009077130?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004171759?sid=102</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 13:00:00 +0900</t>
+          <t>Fri, 24 Jul 2026 13:39:00 +0900</t>
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/24/0009077130_001_20260724130015189.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/24/0009077130_001_20260724130015189.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4968,21 +4970,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>** 황인홍 무주군수, 전북포럼서 방위산업 육성 전략 발제</t>
+          <t>** [뉴스1전북포럼] &amp;quot;전북 방산 육성, 인재·시험평가·실증 기반 갖춰야&amp;quot;(...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004171759?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009077130?sid=102</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 13:39:00 +0900</t>
+          <t>Fri, 24 Jul 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/24/0009077130_001_20260724130015189.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/24/0009077130_001_20260724130015189.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
+          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
+          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
+          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
+          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=887083</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
+          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
+          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
+          <t>https://sjbnews.com/news/news.php?number=887083</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
+          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -942,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
+          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
+          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -966,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
+          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -990,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
+          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1014,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
+          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1038,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
+          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1062,23 +1062,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
+          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+        </is>
+      </c>
+      <c r="E27">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1087,22 +1086,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
+          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E28">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
-        <v/>
+          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1111,21 +1111,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
+          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
+          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1135,21 +1135,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
+          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
+          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1159,21 +1159,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
+          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
+          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1183,21 +1183,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
+          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
+          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1207,21 +1207,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
+          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
+          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
+          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
+          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
+          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
+          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1255,21 +1255,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
+          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
+          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
+        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1279,21 +1279,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
+          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://hbnpress.com/news/view/1065597442480538</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
         <v/>
       </c>
     </row>
@@ -1303,21 +1303,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
+          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
+          <t>https://hbnpress.com/news/view/1065597442480538</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
+        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1327,21 +1327,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
+          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
+          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1351,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
+          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
+          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1375,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
+          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
+          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
+          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
+          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
+          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
+          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
+          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
+          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1495,21 +1495,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
+          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
+          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
+          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1543,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
+          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
+          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
         <v/>
       </c>
     </row>
@@ -1567,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
+          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
+          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
+          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1615,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
+          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1639,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
+          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
+          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1663,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
+          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
+          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1687,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
+          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260819500013</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
+          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260909031119", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260909031119"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1711,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
+          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
+          <t>https://www.viva100.com/article/20260819500013</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260910030722", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260910030722"))</f>
         <v/>
       </c>
     </row>
@@ -1735,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
+          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260817500461</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260909031130", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260909031130"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1759,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
+          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
+          <t>https://www.viva100.com/article/20260817500461</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
+          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260910030736", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260910030736"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
+          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
+          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1807,21 +1807,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>전북대학교, 세계 명문대·글로벌 기업 손잡고 '글로벌 산학연 허브' 도...</t>
+          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208484</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 20:30:00 +0900</t>
+          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208484_477348_3537_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208484_477348_3537_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2383,21 +2383,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
+          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260726500503</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
+          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260909031244", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260909031244"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2407,21 +2407,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
+          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
+          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2431,21 +2431,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
+          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
+          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2455,21 +2455,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
+          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
+          <t>https://www.viva100.com/article/20260812500685</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
+          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260910030903", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260910030903"))</f>
         <v/>
       </c>
     </row>
@@ -2479,21 +2479,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
+          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260812500685</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260909031252", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260909031252"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2503,21 +2503,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
+          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2527,21 +2527,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
+          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
+          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
         <v/>
       </c>
     </row>
@@ -2551,21 +2551,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
+          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
+          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2575,21 +2575,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
+          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
+          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2599,21 +2599,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
+          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
+          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2623,21 +2623,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
+          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2647,21 +2647,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
+          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2671,21 +2671,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
+          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
+          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2695,21 +2695,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
+          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
+          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2719,21 +2719,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
+          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
+          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
         <v/>
       </c>
     </row>
@@ -2743,21 +2743,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
+          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
+          <t>https://www.viva100.com/article/20260726500503</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
+          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260910030934", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260910030934"))</f>
         <v/>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260909031353", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260909031353"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260910031013", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260910031013"))</f>
         <v/>
       </c>
     </row>
@@ -3440,12 +3440,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4173,10 +4173,9 @@
           <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+      <c r="E156">
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -4833,21 +4832,21 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>K-방산, 캐나다서 아쉬운 고배…나토 시장 공략 숙제 남겼다</t>
+          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260707010002482</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 14:30:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E184">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/08d/2026070701000473600024821.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/08d/2026070701000473600024821.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4857,44 +4856,20 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
+          <t>[본지-대교협 공동기획中] 생성형 AI 기반 수업 혁신 확산 속 &amp;quot;인간 고유...</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=593399</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
+          <t>Mon, 15 Jun 2026 09:00:00 +0900</t>
         </is>
       </c>
       <c r="E185">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>[본지-대교협 공동기획中] 생성형 AI 기반 수업 혁신 확산 속 &amp;quot;인간 고유...</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=593399</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Mon, 15 Jun 2026 09:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E186">
         <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg"))</f>
         <v/>
       </c>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260910030722", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260910030722"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260911025725", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260911025725"))</f>
         <v/>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260910030736", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260910030736"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260911025736", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260911025736"))</f>
         <v/>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260910030903", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260910030903"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260911025847", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260911025847"))</f>
         <v/>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260910030934", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260910030934"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260911025914", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260911025914"))</f>
         <v/>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260910031013", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260910031013"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260911025946", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260911025946"))</f>
         <v/>
       </c>
     </row>
@@ -3440,12 +3440,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4173,9 +4173,10 @@
           <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
-      <c r="E156">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
-        <v/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -4869,9 +4870,10 @@
           <t>Mon, 15 Jun 2026 09:00:00 +0900</t>
         </is>
       </c>
-      <c r="E185">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg"))</f>
-        <v/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,9 +547,10 @@
           <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
         </is>
       </c>
-      <c r="E5">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
-        <v/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -798,21 +799,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>** 전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
+          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +823,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>** 전북대 “K-방산 인재·산업 거점으로 도약”</t>
+          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -846,22 +847,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>** 전북대, 글로벌 방산기업 BAE와 맞손…K-방산 인재 키운다</t>
+          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=442498</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 17:28:00 +0900</t>
-        </is>
-      </c>
-      <c r="E18">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202606/442498_151267_2652_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202606/442498_151267_2652_v150.jpg"))</f>
-        <v/>
+          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -870,22 +872,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
+          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E19">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
-        <v/>
+          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -894,21 +897,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
+          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
+          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
+          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +921,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
+          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=887083</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
+          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -942,22 +945,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
+          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
+          <t>https://sjbnews.com/news/news.php?number=887083</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E22">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
-        <v/>
+          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -966,21 +970,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
+          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
+          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -990,21 +994,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
+          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1014,21 +1018,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
+          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1038,21 +1042,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
+          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1062,21 +1066,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
+          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1086,17 +1090,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
+          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1111,22 +1115,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
+          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E29">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
-        <v/>
+          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1135,21 +1140,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
+          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
+          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1159,21 +1164,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
+          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
+          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1183,21 +1188,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
+          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
+          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1207,21 +1212,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
+          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
+          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1231,21 +1236,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
+          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
+          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
+          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1255,21 +1260,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
+          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
+          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
+          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1279,21 +1284,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
+          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
+          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
+        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1303,21 +1308,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
+          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://hbnpress.com/news/view/1065597442480538</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
         <v/>
       </c>
     </row>
@@ -1327,21 +1332,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
+          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
+          <t>https://hbnpress.com/news/view/1065597442480538</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
+        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1351,21 +1356,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
+          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
+          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1375,21 +1380,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
+          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
+          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1404,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
+          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
+          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1428,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
+          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1452,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
+          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1476,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
+          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
+          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1495,21 +1500,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
+          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
+          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1524,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
+          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
+          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
         <v/>
       </c>
     </row>
@@ -1543,21 +1548,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
+          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1567,21 +1572,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
+          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
+          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
         <v/>
       </c>
     </row>
@@ -1591,21 +1596,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
+          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
+          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1615,21 +1620,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
+          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1639,21 +1644,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
+          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1663,21 +1668,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
+          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
+          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1687,21 +1692,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
+          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
+          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1711,21 +1716,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
+          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260819500013</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
+          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260911025725", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260911025725"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1735,21 +1740,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
+          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
+          <t>https://www.viva100.com/article/20260819500013</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260912025959", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260912025959"))</f>
         <v/>
       </c>
     </row>
@@ -1759,21 +1764,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
+          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260817500461</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260911025736", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260911025736"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1788,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
+          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
+          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1807,21 +1812,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
+          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
+          <t>https://www.ajunews.com/view/20260908164442351</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
+          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1831,21 +1836,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
+          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260908164442351</t>
+          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
+          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1855,21 +1860,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
+          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
+          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1879,21 +1884,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
+          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
+          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1903,21 +1908,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
+          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
+          <t>https://www.viva100.com/article/20260817500461</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
+          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260912030025", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260912030025"))</f>
         <v/>
       </c>
     </row>
@@ -1927,21 +1932,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
+          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
+          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1951,21 +1956,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
+          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
+          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1975,21 +1980,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
+          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260806162915186</t>
+          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
+          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +2004,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
+          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
+          <t>https://www.ajunews.com/view/20260806162915186</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
+          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2023,21 +2028,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
+          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
+          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
+          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2047,21 +2052,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
+          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2076,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
+          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
+          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
+          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
+        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2100,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
+          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2124,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
+          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2143,21 +2148,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
+          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -2167,21 +2172,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
+          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607290020</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2191,21 +2196,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
+          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
+          <t>https://www.betanews.net/article/view/beta202607290020</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2215,21 +2220,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
+          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
+          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2239,21 +2244,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
+          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2263,21 +2268,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
+          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
+          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2287,21 +2292,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
+          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
+          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2311,21 +2316,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
+          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
+          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2335,21 +2340,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
+          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
+          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2359,21 +2364,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>고려대-전북대 국가균형발전 이끄는 산/학/연 협력 허브 구축 협약</t>
+          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621016</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 13:50:00 +0900</t>
+          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621016_534040_4114_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621016_534040_4114_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2383,21 +2388,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
+          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
+          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2407,21 +2412,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
+          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
+          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2431,21 +2436,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
+          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
+          <t>https://www.viva100.com/article/20260812500685</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
+          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260912030142", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260912030142"))</f>
         <v/>
       </c>
     </row>
@@ -2455,21 +2460,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
+          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260812500685</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260911025847", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260911025847"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2479,21 +2484,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
+          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2503,21 +2508,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
+          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
+          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
         <v/>
       </c>
     </row>
@@ -2527,21 +2532,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
+          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
+          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2551,21 +2556,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
+          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
+          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2575,21 +2580,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
+          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
+          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2599,21 +2604,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
+          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2623,21 +2628,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
+          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2647,21 +2652,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
+          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
+          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2671,21 +2676,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
+          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
+          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2695,21 +2700,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
+          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
+          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
         <v/>
       </c>
     </row>
@@ -2719,21 +2724,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
+          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
+          <t>https://www.viva100.com/article/20260726500503</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
+          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260912030219", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260912030219"))</f>
         <v/>
       </c>
     </row>
@@ -2743,21 +2748,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
+          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260726500503</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260911025914", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260911025914"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2767,21 +2772,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
+          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2791,21 +2796,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
+          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
+          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2815,21 +2820,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
+          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
+          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2839,21 +2844,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
+          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
+          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2863,21 +2868,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
+          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
+          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2887,21 +2892,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
+          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
+          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2911,21 +2916,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
+          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
+          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
+          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
+        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2935,21 +2940,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
+          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260714135200349</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
+          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2959,21 +2964,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
+          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
+          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2983,21 +2988,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
+          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
+          <t>https://www.ajunews.com/view/20260714135200349</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
+          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
         <v/>
       </c>
     </row>
@@ -3007,21 +3012,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
+          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
+          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
+          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3031,21 +3036,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
+          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
+          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3055,21 +3060,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
+          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
+          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3079,21 +3084,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
+          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260712500414</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
+          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260911025946", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260911025946"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3103,23 +3108,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
+          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
+        </is>
+      </c>
+      <c r="E112">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -3128,21 +3132,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
+          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
+          <t>https://www.viva100.com/article/20260712500414</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
+          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260912030256", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260912030256"))</f>
         <v/>
       </c>
     </row>
@@ -3152,21 +3156,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
+          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260709500128</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
+          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3176,21 +3180,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
+          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
+          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3200,21 +3204,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
+          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
+          <t>https://www.news2day.co.kr/article/20260709500128</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
         <v/>
       </c>
     </row>
@@ -3224,21 +3228,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
+          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
+          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
+          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3248,21 +3252,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
+          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3272,21 +3276,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
+          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3296,21 +3300,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
+          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
+          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3320,21 +3324,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
+          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3344,21 +3348,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
+          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3368,21 +3372,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
+          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
+          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3392,21 +3396,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
+          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3416,21 +3420,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>&amp;quot;방산 기술·MRO 합친 '패키지 수출' 늘려야&amp;quot;</t>
+          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005304632?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 17:32:00 +0900</t>
+          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3440,21 +3444,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3464,21 +3468,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>&amp;quot;방산 기술·MRO 합친 '패키지 수출' 늘려야&amp;quot;</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005304632?sid=101</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Tue, 30 Jun 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3488,21 +3492,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
+          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
+          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3512,21 +3516,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3536,21 +3540,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3560,21 +3564,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
+          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
+          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3584,21 +3588,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
+          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
+          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3608,21 +3612,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
+          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
+          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3632,21 +3636,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
+          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
+          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3656,21 +3660,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
+          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://www.jjan.kr/article/20260614500064</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
+          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3680,21 +3684,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
+          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
+          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3704,21 +3708,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3728,21 +3732,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -3752,21 +3756,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://www.jjan.kr/article/20260614500064</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3776,21 +3780,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3800,21 +3804,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3824,21 +3828,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3848,21 +3852,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3872,21 +3876,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3896,21 +3900,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>추미애, 핵심 공약 직접 챙긴다</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 17:08:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3920,21 +3924,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3944,21 +3948,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3968,21 +3972,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3992,21 +3996,21 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>추미애, 핵심 공약 직접 챙긴다</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Fri, 01 May 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E149">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4016,21 +4020,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E150">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4040,21 +4044,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E151">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4064,21 +4068,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E152">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4088,21 +4092,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E153">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4112,21 +4116,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E154">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4136,21 +4140,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
         </is>
       </c>
       <c r="E155">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4160,23 +4164,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E156">
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -4185,21 +4188,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E157">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4209,21 +4212,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E158">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4233,21 +4236,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E159">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4257,21 +4260,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E160">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4281,21 +4284,21 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E161">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4305,21 +4308,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E162">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4329,21 +4332,21 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E163">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4353,21 +4356,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
         </is>
       </c>
       <c r="E164">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4377,21 +4380,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
         </is>
       </c>
       <c r="E165">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4401,21 +4404,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
         </is>
       </c>
       <c r="E166">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4425,21 +4428,21 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
         </is>
       </c>
       <c r="E167">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4449,21 +4452,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E168">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4473,21 +4476,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E169">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4497,21 +4500,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E170">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4521,21 +4524,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E171">
-        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4545,21 +4548,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E172">
-        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4569,21 +4572,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E173">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4593,21 +4596,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
+          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
+          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
         </is>
       </c>
       <c r="E174">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4617,21 +4620,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
+          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
+          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
+          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
         </is>
       </c>
       <c r="E175">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4641,21 +4644,21 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
+          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2605457</t>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
+          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E176">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
+        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4665,21 +4668,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
+          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
+          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E177">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4689,21 +4692,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
+          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
         </is>
       </c>
       <c r="E178">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4713,21 +4716,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
+          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
+          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
         </is>
       </c>
       <c r="E179">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4737,21 +4740,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
+          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
+          <t>https://www.etoday.co.kr/news/view/2605457</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
+          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
         </is>
       </c>
       <c r="E180">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
         <v/>
       </c>
     </row>
@@ -4761,21 +4764,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
+          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
+          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E181">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4785,21 +4788,21 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>성능보다 우선한 '동맹'…캐나다, 왜 독일 선택했나?</t>
+          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000625036?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 21:20:00 +0900</t>
+          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
         </is>
       </c>
       <c r="E182">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4809,21 +4812,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>나토 국방비 증액에도 생산 병목…기회 잡는 K-방산</t>
+          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>http://www.metroseoul.co.kr/article/20260707500477</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:54:00 +0900</t>
+          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
         </is>
       </c>
       <c r="E183">
-        <f>HYPERLINK("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg", IMAGE("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4833,21 +4836,21 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
+          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
+          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E184">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4857,23 +4860,119 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
+          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E185">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>성능보다 우선한 '동맹'…캐나다, 왜 독일 선택했나?</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/448/0000625036?sid=101</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 21:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E186">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>나토 국방비 증액에도 생산 병목…기회 잡는 K-방산</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>http://www.metroseoul.co.kr/article/20260707500477</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 16:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E188">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
           <t>[본지-대교협 공동기획中] 생성형 AI 기반 수업 혁신 확산 속 &amp;quot;인간 고유...</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>https://news.unn.net/news/articleView.html?idxno=593399</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 09:00:00 +0900</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+      <c r="E189">
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,21 +462,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>** 전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
+          <t>** 전북대학교 계약정원제 사업, 우주항공·AI·첨단방산 미래인재 양성 '비...</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=210469</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
+          <t>Sat, 12 Sep 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -486,21 +486,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
+          <t>** 전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
+          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -510,21 +510,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
+          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
+          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -534,23 +534,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
+          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=884391</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E5">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -559,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
+          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
+          <t>https://sjbnews.com/news/news.php?number=884391</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
+          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -583,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
+          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
+          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -607,21 +606,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
+          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
+          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -631,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
+          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
+          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -655,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
+          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -679,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
+          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -703,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
+          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
+          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -727,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
+          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
+          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -751,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
+          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -775,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>** 전북대, 한화·현대로템·보잉 등 임원 객원교수 초빙…방산 인재양성 ...</t>
+          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607300039</t>
+          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:10:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg"))</f>
+        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -799,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
+          <t>** 전북대, 한화·현대로템·보잉 등 임원 객원교수 초빙…방산 인재양성 ...</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
+          <t>https://www.betanews.net/article/view/beta202607300039</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -823,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
+          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -847,23 +846,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
+          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
+        </is>
+      </c>
+      <c r="E18">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -872,23 +870,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
+          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -897,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
+          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -921,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
+          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
+          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
+          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -945,23 +942,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
+          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=887083</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E22">
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -970,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
+          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
+          <t>https://sjbnews.com/news/news.php?number=887083</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
+          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -994,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
+          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
+          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1018,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
+          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1042,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
+          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1066,21 +1062,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
+          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1090,23 +1086,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
+          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E28">
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1115,23 +1110,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
+          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+        </is>
+      </c>
+      <c r="E29">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1140,22 +1134,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
+          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E30">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
-        <v/>
+          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1164,21 +1159,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
+          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
+          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1188,21 +1183,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
+          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
+          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1212,21 +1207,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
+          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
+          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1236,21 +1231,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
+          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
+          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1260,21 +1255,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
+          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
+          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
+          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1284,21 +1279,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
+          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
+          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
+          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1308,21 +1303,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
+          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
+          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
+        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1332,21 +1327,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
+          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://hbnpress.com/news/view/1065597442480538</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
         <v/>
       </c>
     </row>
@@ -1356,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
+          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
+          <t>https://hbnpress.com/news/view/1065597442480538</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
+        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1380,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
+          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
+          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1404,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
+          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
+          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1428,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
+          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
+          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1452,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
+          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1476,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
+          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1500,21 +1495,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
+          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
+          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1524,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
+          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
+          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1548,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
+          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
+          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
         <v/>
       </c>
     </row>
@@ -1572,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
+          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1596,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
+          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
+          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
         <v/>
       </c>
     </row>
@@ -1620,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
+          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
+          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1644,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
+          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1668,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
+          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1692,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
+          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
+          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1716,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
+          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
+          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1740,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
+          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260819500013</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
+          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260912025959", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260912025959"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1764,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
+          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
+          <t>https://www.viva100.com/article/20260819500013</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260913023146", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260913023146"))</f>
         <v/>
       </c>
     </row>
@@ -1788,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
+          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1812,21 +1807,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
+          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260908164442351</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
+          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1836,21 +1831,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
+          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
+          <t>https://www.ajunews.com/view/20260908164442351</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
+          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1860,21 +1855,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
+          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
+          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
+          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1884,21 +1879,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
+          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
+          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1908,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
+          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260817500461</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
+          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260912030025", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260912030025"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1932,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
+          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
+          <t>https://www.viva100.com/article/20260817500461</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
+          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260913023216", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260913023216"))</f>
         <v/>
       </c>
     </row>
@@ -1956,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
+          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
+          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1980,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
+          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
+          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2004,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
+          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260806162915186</t>
+          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
+          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2028,21 +2023,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
+          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
+          <t>https://www.ajunews.com/view/20260806162915186</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
+          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2052,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
+          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
+          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
+          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2076,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
+          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2100,21 +2095,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
+          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
+          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
+          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
+        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2124,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
+          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2148,21 +2143,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
+          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2172,21 +2167,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
+          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -2196,21 +2191,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
+          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607290020</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2220,21 +2215,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
+          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
+          <t>https://www.betanews.net/article/view/beta202607290020</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2244,21 +2239,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
+          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
+          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2268,21 +2263,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
+          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2292,21 +2287,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
+          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
+          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2316,21 +2311,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
+          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
+          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2340,21 +2335,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
+          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
+          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2364,21 +2359,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
+          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2388,21 +2383,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
+          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
+          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2412,21 +2407,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
+          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
+          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2436,21 +2431,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
+          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260812500685</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
+          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260912030142", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260912030142"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2460,21 +2455,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
+          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
+          <t>https://www.viva100.com/article/20260812500685</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
+          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260913023332", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260913023332"))</f>
         <v/>
       </c>
     </row>
@@ -2484,21 +2479,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
+          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2508,21 +2503,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
+          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2532,21 +2527,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
+          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
+          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
         <v/>
       </c>
     </row>
@@ -2556,21 +2551,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
+          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
+          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2580,21 +2575,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
+          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
+          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2604,21 +2599,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
+          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
+          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2628,21 +2623,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
+          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2652,21 +2647,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
+          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2676,21 +2671,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
+          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
+          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2700,21 +2695,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
+          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
+          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
+          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2724,21 +2719,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
+          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260726500503</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
+          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260912030219", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260912030219"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
         <v/>
       </c>
     </row>
@@ -2748,21 +2743,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
+          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
+          <t>https://www.viva100.com/article/20260726500503</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
+          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260913023405", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260913023405"))</f>
         <v/>
       </c>
     </row>
@@ -2796,21 +2791,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
+          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2820,21 +2815,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
+          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
+          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2844,21 +2839,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
+          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
+          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2868,21 +2863,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
+          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
+          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2892,21 +2887,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
+          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
+          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2916,21 +2911,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
+          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
+          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2940,21 +2935,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
+          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
+          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
+          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
+        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2964,21 +2959,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
+          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
+          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2988,21 +2983,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
+          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260714135200349</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
+          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3012,21 +3007,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
+          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
+          <t>https://www.ajunews.com/view/20260714135200349</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
+          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
         <v/>
       </c>
     </row>
@@ -3036,21 +3031,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
+          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
+          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
+          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3060,21 +3055,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
+          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
+          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3084,21 +3079,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
+          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
+          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
+          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3108,21 +3103,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
+          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
+          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3132,21 +3127,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
+          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260712500414</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
+          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260912030256", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260912030256"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3156,21 +3151,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
+          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
+          <t>https://www.viva100.com/article/20260712500414</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
+          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260913023450", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260913023450"))</f>
         <v/>
       </c>
     </row>
@@ -3180,22 +3175,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
+          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
-        </is>
-      </c>
-      <c r="E115">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -3204,21 +3200,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
+          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260709500128</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
+          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3228,21 +3224,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
+          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
+          <t>https://www.news2day.co.kr/article/20260709500128</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
+          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
         <v/>
       </c>
     </row>
@@ -3252,21 +3248,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
+          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3276,21 +3272,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
+          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3300,21 +3296,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
+          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3324,21 +3320,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
+          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
+          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3348,21 +3344,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
+          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3372,21 +3368,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
+          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3396,21 +3392,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
+          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
+          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3420,21 +3416,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
+          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3444,21 +3440,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
+          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
+          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3468,21 +3464,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>&amp;quot;방산 기술·MRO 합친 '패키지 수출' 늘려야&amp;quot;</t>
+          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005304632?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 17:32:00 +0900</t>
+          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3492,21 +3488,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
+          <t>&amp;quot;방산 기술·MRO 합친 '패키지 수출' 늘려야&amp;quot;</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005304632?sid=101</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
+          <t>Tue, 30 Jun 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3516,21 +3512,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3564,21 +3560,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3588,21 +3584,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
+          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
+          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3612,21 +3608,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
+          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
+          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3636,21 +3632,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
+          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
+          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3660,21 +3656,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
+          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
+          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3684,21 +3680,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
+          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
+          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3708,21 +3704,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
+          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
+          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3732,21 +3728,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
+          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
+          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
+          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3756,21 +3752,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
+          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://www.jjan.kr/article/20260614500064</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
+          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -3780,21 +3776,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
+          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
+          <t>https://www.jjan.kr/article/20260614500064</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
+          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3804,21 +3800,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3828,21 +3824,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3852,21 +3848,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3876,21 +3872,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3900,21 +3896,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3924,21 +3920,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3948,21 +3944,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3972,21 +3968,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3996,21 +3992,21 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>추미애, 핵심 공약 직접 챙긴다</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 17:08:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E149">
-        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4020,21 +4016,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>추미애, 핵심 공약 직접 챙긴다</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Fri, 01 May 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E150">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4044,21 +4040,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E151">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4068,21 +4064,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E152">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4092,21 +4088,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E153">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4116,21 +4112,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E154">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4140,21 +4136,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E155">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4164,21 +4160,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
         </is>
       </c>
       <c r="E156">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4188,21 +4184,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E157">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4212,21 +4208,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E158">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4236,21 +4232,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E159">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4260,21 +4256,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E160">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4284,22 +4280,23 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
-        </is>
-      </c>
-      <c r="E161">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
-        <v/>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -4308,21 +4305,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E162">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4332,21 +4329,21 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E163">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4356,21 +4353,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E164">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4380,21 +4377,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
+          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
+          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
+          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
         </is>
       </c>
       <c r="E165">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4404,21 +4401,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
+          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
+          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
         </is>
       </c>
       <c r="E166">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4428,21 +4425,21 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
+          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
+          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
         </is>
       </c>
       <c r="E167">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4452,21 +4449,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
         </is>
       </c>
       <c r="E168">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4476,21 +4473,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E169">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4500,21 +4497,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E170">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4524,21 +4521,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E171">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4548,21 +4545,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E172">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4572,21 +4569,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E173">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4596,21 +4593,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E174">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4620,21 +4617,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
+          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
+          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
         </is>
       </c>
       <c r="E175">
-        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4644,21 +4641,21 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
+          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
+          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
+          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
         </is>
       </c>
       <c r="E176">
-        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4668,21 +4665,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
+          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
+          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E177">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4692,21 +4689,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
+          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
+          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E178">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4716,21 +4713,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
+          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
         </is>
       </c>
       <c r="E179">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4740,21 +4737,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
+          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2605457</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
+          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
         </is>
       </c>
       <c r="E180">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4764,22 +4761,23 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
+          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
+          <t>https://www.etoday.co.kr/news/view/2605457</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E181">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
-        <v/>
+          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -4788,21 +4786,21 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
+          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
+          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E182">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4812,21 +4810,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
+          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
+          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
         </is>
       </c>
       <c r="E183">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4836,21 +4834,21 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
+          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
+          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
         </is>
       </c>
       <c r="E184">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4860,21 +4858,21 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
+          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
+          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E185">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4884,21 +4882,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>성능보다 우선한 '동맹'…캐나다, 왜 독일 선택했나?</t>
+          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000625036?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 21:20:00 +0900</t>
+          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E186">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4908,23 +4906,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>나토 국방비 증액에도 생산 병목…기회 잡는 K-방산</t>
+          <t>성능보다 우선한 '동맹'…캐나다, 왜 독일 선택했나?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>http://www.metroseoul.co.kr/article/20260707500477</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000625036?sid=101</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:54:00 +0900</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 07 Jul 2026 21:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E187">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="188">
@@ -4933,22 +4930,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
+          <t>나토 국방비 증액에도 생산 병목…기회 잡는 K-방산</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
+          <t>http://www.metroseoul.co.kr/article/20260707500477</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E188">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
-        <v/>
+          <t>Tue, 07 Jul 2026 16:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -4957,20 +4955,44 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
+          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E189">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
           <t>[본지-대교협 공동기획中] 생성형 AI 기반 수업 혁신 확산 속 &amp;quot;인간 고유...</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>https://news.unn.net/news/articleView.html?idxno=593399</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 09:00:00 +0900</t>
         </is>
       </c>
-      <c r="E189">
+      <c r="E190">
         <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg"))</f>
         <v/>
       </c>
@@ -5179,9 +5201,10 @@
           <t>Tue, 21 Jul 2026 09:18:00 +0900</t>
         </is>
       </c>
-      <c r="E8">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png"))</f>
-        <v/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="9">

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -534,21 +534,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
+          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
+          <t>https://sjbnews.com/news/news.php?number=884391</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
+          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -558,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
+          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=884391</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
+          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
+          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
+          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -606,21 +606,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
+          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
+          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
+          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
+          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
+          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
+          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
+          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
+          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
+          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
+          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
+          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
+          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
+          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
+          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
+          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
+          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
+          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
+          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
+          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -942,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
+          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
+          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
+          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -966,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
+          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=887083</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
+          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -990,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
+          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
+          <t>https://sjbnews.com/news/news.php?number=887083</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
+          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1014,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
+          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
+          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1038,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
+          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1062,21 +1062,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
+          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1086,21 +1086,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
+          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1110,21 +1110,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
+          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1134,23 +1134,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
+          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+        </is>
+      </c>
+      <c r="E30">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1159,22 +1158,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
+          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E31">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
-        <v/>
+          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1183,21 +1183,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
+          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
+          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1207,21 +1207,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
+          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
+          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
+          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
+          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1255,21 +1255,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
+          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
+          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1279,21 +1279,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
+          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
+          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
+          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1303,21 +1303,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
+          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
+          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
+          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1327,21 +1327,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
+          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
+          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
+        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1351,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
+          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://hbnpress.com/news/view/1065597442480538</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
         <v/>
       </c>
     </row>
@@ -1375,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
+          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
+          <t>https://hbnpress.com/news/view/1065597442480538</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
+        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
+          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
+          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
+          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
+          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
+          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
+          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
+          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1495,21 +1495,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
+          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
+          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
+          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1543,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
+          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
+          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1567,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
+          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
+          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
         <v/>
       </c>
     </row>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
+          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1615,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
+          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
+          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
         <v/>
       </c>
     </row>
@@ -1639,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
+          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
+          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1663,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
+          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1687,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
+          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1711,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
+          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
+          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1735,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
+          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
+          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1759,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
+          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260819500013</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
+          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260913023146", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260913023146"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
+          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
+          <t>https://www.viva100.com/article/20260819500013</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260914024733", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260914024733"))</f>
         <v/>
       </c>
     </row>
@@ -1807,21 +1807,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
+          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1831,21 +1831,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
+          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260908164442351</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
+          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1855,21 +1855,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
+          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
+          <t>https://www.ajunews.com/view/20260908164442351</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
+          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1879,21 +1879,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
+          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
+          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
+          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1903,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
+          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
+          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1927,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
+          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260817500461</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
+          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260913023216", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260913023216"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1951,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
+          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
+          <t>https://www.viva100.com/article/20260817500461</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
+          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260914024752", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260914024752"))</f>
         <v/>
       </c>
     </row>
@@ -1975,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
+          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
+          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
+          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
+          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2023,21 +2023,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
+          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260806162915186</t>
+          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
+          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2047,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
+          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
+          <t>https://www.ajunews.com/view/20260806162915186</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
+          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
+          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
+          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
+          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2095,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
+          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
+          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
+          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
+          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
+        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2143,21 +2143,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
+          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2167,21 +2167,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
+          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2191,21 +2191,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
+          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -2215,21 +2215,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
+          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607290020</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2239,21 +2239,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
+          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
+          <t>https://www.betanews.net/article/view/beta202607290020</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2263,21 +2263,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
+          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
+          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2287,21 +2287,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
+          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2311,21 +2311,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
+          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
+          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2335,21 +2335,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
+          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
+          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2359,21 +2359,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
+          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
+          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2383,21 +2383,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
+          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2407,21 +2407,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
+          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
+          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2431,21 +2431,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
+          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
+          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2455,21 +2455,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
+          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260812500685</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
+          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260913023332", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260913023332"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2479,21 +2479,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
+          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
+          <t>https://www.viva100.com/article/20260812500685</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
+          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260914024856", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260914024856"))</f>
         <v/>
       </c>
     </row>
@@ -2503,21 +2503,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
+          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2527,21 +2527,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
+          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2551,21 +2551,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
+          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
+          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
         <v/>
       </c>
     </row>
@@ -2575,21 +2575,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
+          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
+          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2599,21 +2599,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
+          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
+          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2623,21 +2623,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
+          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
+          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2647,21 +2647,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
+          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2671,21 +2671,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
+          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2695,21 +2695,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
+          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
+          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2719,21 +2719,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
+          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
+          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
+          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2743,21 +2743,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
+          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260726500503</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
+          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260913023405", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260913023405"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
         <v/>
       </c>
     </row>
@@ -2767,21 +2767,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
+          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
+          <t>https://www.viva100.com/article/20260726500503</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
+          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260914024925", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260914024925"))</f>
         <v/>
       </c>
     </row>
@@ -2815,21 +2815,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
+          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2839,21 +2839,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
+          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
+          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2863,21 +2863,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
+          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
+          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2887,21 +2887,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
+          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
+          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2911,21 +2911,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
+          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
+          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2935,21 +2935,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
+          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
+          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2959,21 +2959,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
+          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
+          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
+          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
+        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2983,21 +2983,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
+          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
+          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3007,21 +3007,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
+          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260714135200349</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
+          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3031,21 +3031,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
+          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
+          <t>https://www.ajunews.com/view/20260714135200349</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
+          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
         <v/>
       </c>
     </row>
@@ -3055,21 +3055,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
+          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
+          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
+          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3079,21 +3079,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
+          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
+          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3103,21 +3103,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
+          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
+          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
+          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3127,21 +3127,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
+          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
+          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3151,21 +3151,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
+          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260712500414</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
+          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260913023450", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260913023450"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3175,23 +3175,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
+          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
+          <t>https://www.viva100.com/article/20260712500414</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E115">
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260914025000", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260914025000"))</f>
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -3200,22 +3199,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
+          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
-        </is>
-      </c>
-      <c r="E116">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -3224,21 +3224,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
+          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260709500128</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
+          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3248,21 +3248,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
+          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
+          <t>https://www.news2day.co.kr/article/20260709500128</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
+          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
         <v/>
       </c>
     </row>
@@ -3272,21 +3272,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
+          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3296,21 +3296,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
+          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3320,21 +3320,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
+          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3344,21 +3344,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
+          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
+          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3368,21 +3368,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
+          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3392,21 +3392,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
+          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3416,21 +3416,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
+          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
+          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3440,21 +3440,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
+          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3464,21 +3464,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
+          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
+          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3488,21 +3488,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>&amp;quot;방산 기술·MRO 합친 '패키지 수출' 늘려야&amp;quot;</t>
+          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005304632?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 17:32:00 +0900</t>
+          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3512,21 +3512,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
+          <t>&amp;quot;방산 기술·MRO 합친 '패키지 수출' 늘려야&amp;quot;</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
+          <t>https://n.news.naver.com/mnews/article/015/0005304632?sid=101</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
+          <t>Tue, 30 Jun 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3536,21 +3536,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3608,21 +3608,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
+          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
+          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3632,21 +3632,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
+          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
+          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3656,21 +3656,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
+          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
+          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3680,21 +3680,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
+          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
+          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3704,21 +3704,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
+          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
+          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3728,21 +3728,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
+          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
+          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3752,21 +3752,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
+          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
+          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
+          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3776,21 +3776,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
+          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://www.jjan.kr/article/20260614500064</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
+          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -3800,21 +3800,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
+          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
+          <t>https://www.jjan.kr/article/20260614500064</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
+          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3824,21 +3824,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3848,21 +3848,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3872,21 +3872,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3896,21 +3896,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3920,21 +3920,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3968,21 +3968,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3992,21 +3992,21 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E149">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4016,21 +4016,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>추미애, 핵심 공약 직접 챙긴다</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 17:08:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E150">
-        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4040,21 +4040,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>추미애, 핵심 공약 직접 챙긴다</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Fri, 01 May 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E151">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4064,21 +4064,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E152">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4088,21 +4088,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E153">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4112,21 +4112,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E154">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4136,21 +4136,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E155">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4160,21 +4160,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E156">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4184,21 +4184,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
         </is>
       </c>
       <c r="E157">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4208,21 +4208,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E158">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4232,21 +4232,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E159">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4256,21 +4256,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E160">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4280,23 +4280,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+        </is>
+      </c>
+      <c r="E161">
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="162">
@@ -4305,21 +4304,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E162">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4329,21 +4328,21 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E163">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4353,21 +4352,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E164">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4377,21 +4376,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E165">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4401,21 +4400,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
+          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
+          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
+          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
         </is>
       </c>
       <c r="E166">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4425,21 +4424,21 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
+          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
+          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
         </is>
       </c>
       <c r="E167">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4449,21 +4448,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
+          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
+          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
         </is>
       </c>
       <c r="E168">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4473,21 +4472,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
         </is>
       </c>
       <c r="E169">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4497,21 +4496,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E170">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4521,21 +4520,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E171">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4545,21 +4544,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E172">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4569,21 +4568,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E173">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4593,21 +4592,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E174">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4617,21 +4616,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>전북대, '첨단산업 인재양성 부트캠프' AI 분야 선정</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=435119</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 20:48:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E175">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202603/435119_144745_4131_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4774,10 +4773,9 @@
           <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+      <c r="E181">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
+        <v/>
       </c>
     </row>
     <row r="182">
@@ -5201,10 +5199,9 @@
           <t>Tue, 21 Jul 2026 09:18:00 +0900</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+      <c r="E8">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png"))</f>
+        <v/>
       </c>
     </row>
     <row r="9">

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260914024733", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260914024733"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260915044134", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260915044134"))</f>
         <v/>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260914024752", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260914024752"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260915044158", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260915044158"))</f>
         <v/>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260914024856", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260914024856"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260915044304", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260915044304"))</f>
         <v/>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260914024925", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260914024925"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260915044337", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260915044337"))</f>
         <v/>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
+          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
+          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260914025000", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260914025000"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260915044418", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260915044418"))</f>
         <v/>
       </c>
     </row>
@@ -3212,10 +3212,9 @@
           <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+      <c r="E116">
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -3560,12 +3559,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3574,7 +3573,7 @@
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3584,12 +3583,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3598,7 +3597,7 @@
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -510,21 +510,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
+          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
+          <t>https://sjbnews.com/news/news.php?number=884391</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
+          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -534,21 +534,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
+          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=884391</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
+          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -558,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
+          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
+          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
+          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
+          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -606,21 +606,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
+          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
+          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
+          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
+          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
+          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
+          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
+          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
+          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
+          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
+          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
+          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
+          <t>K-방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
+          <t>Tue, 15 Sep 2026 16:40:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
+          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
+          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
+          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
+          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
+          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -942,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
+          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -966,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
+          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
+          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
+          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -990,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
+          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=887083</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
+          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1014,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
+          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
+          <t>https://sjbnews.com/news/news.php?number=887083</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
+          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1038,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
+          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
+          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1062,21 +1062,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
+          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1086,21 +1086,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
+          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1110,21 +1110,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
+          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1134,21 +1134,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
+          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1158,23 +1158,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
+          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+        </is>
+      </c>
+      <c r="E31">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1183,22 +1182,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
+          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E32">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
-        <v/>
+          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1207,21 +1207,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
+          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
+          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
+          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
+          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1255,21 +1255,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
+          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
+          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1279,21 +1279,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
+          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
+          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1303,21 +1303,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
+          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
+          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
+          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1327,21 +1327,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
+          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
+          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
+          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1351,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
+          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
+          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
+        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1375,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
+          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://hbnpress.com/news/view/1065597442480538</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
+          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
+          <t>https://hbnpress.com/news/view/1065597442480538</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
+        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
+          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
+          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
+          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
+          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
+          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
+          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1495,21 +1495,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
+          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
+          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1543,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
+          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
+          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1567,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
+          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
+          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
+          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
+          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
         <v/>
       </c>
     </row>
@@ -1615,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
+          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1639,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
+          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
+          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
         <v/>
       </c>
     </row>
@@ -1663,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
+          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
+          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1687,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
+          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1711,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
+          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1735,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
+          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
+          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1759,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
+          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
+          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
+          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260819500013</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
+          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260915044134", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260915044134"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1807,21 +1807,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
+          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
+          <t>https://www.viva100.com/article/20260819500013</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260916033541", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260916033541"))</f>
         <v/>
       </c>
     </row>
@@ -1831,21 +1831,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
+          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1855,21 +1855,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
+          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260908164442351</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
+          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1879,21 +1879,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
+          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
+          <t>https://www.ajunews.com/view/20260908164442351</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
+          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1903,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
+          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
+          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
+          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1927,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
+          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
+          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1951,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
+          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260817500461</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
+          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260915044158", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260915044158"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1975,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
+          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
+          <t>https://www.viva100.com/article/20260817500461</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
+          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260916033608", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260916033608"))</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
+          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
+          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2023,21 +2023,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
+          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
+          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2047,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
+          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260806162915186</t>
+          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
+          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
+          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
+          <t>https://www.ajunews.com/view/20260806162915186</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
+          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2095,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
+          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
+          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
+          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
+          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2143,21 +2143,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
+          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
+          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
+          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
+        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2167,21 +2167,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
+          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2191,21 +2191,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
+          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2215,21 +2215,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
+          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -2239,21 +2239,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
+          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607290020</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2263,21 +2263,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
+          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
+          <t>https://www.betanews.net/article/view/beta202607290020</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2287,21 +2287,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
+          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
+          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2311,21 +2311,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
+          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2335,21 +2335,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
+          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
+          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2359,21 +2359,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
+          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
+          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2383,21 +2383,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
+          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
+          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260915044304", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260915044304"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260916033734", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260916033734"))</f>
         <v/>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260915044337", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260915044337"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260916033810", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260916033810"))</f>
         <v/>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
+          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
+          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260915044418", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260915044418"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260916033900", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260916033900"))</f>
         <v/>
       </c>
     </row>
@@ -3511,21 +3511,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>&amp;quot;방산 기술·MRO 합친 '패키지 수출' 늘려야&amp;quot;</t>
+          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/015/0005304632?sid=101</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 17:32:00 +0900</t>
+          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/015/2026/06/30/0005304632_001_20260701004912623.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3535,21 +3535,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3583,21 +3583,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3607,21 +3607,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
+          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
+          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3631,21 +3631,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
+          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
+          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3655,21 +3655,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
+          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
+          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3679,21 +3679,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
+          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
+          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3703,21 +3703,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
+          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
+          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3727,21 +3727,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
+          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
+          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
+          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3751,21 +3751,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
+          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
+          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -3775,21 +3775,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
+          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
+          <t>https://www.jjan.kr/article/20260614500064</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
+          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3799,21 +3799,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
+          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://www.jjan.kr/article/20260614500064</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
+          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3823,21 +3823,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3847,21 +3847,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3871,21 +3871,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3895,21 +3895,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3919,21 +3919,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3943,21 +3943,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3967,21 +3967,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3991,21 +3991,21 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E149">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4015,21 +4015,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>추미애, 핵심 공약 직접 챙긴다</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Fri, 01 May 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E150">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4039,21 +4039,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>추미애, 핵심 공약 직접 챙긴다</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 17:08:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E151">
-        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4063,21 +4063,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E152">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4087,21 +4087,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E153">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4111,21 +4111,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E154">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4135,21 +4135,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E155">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4159,21 +4159,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
         </is>
       </c>
       <c r="E156">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4183,21 +4183,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E157">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4207,21 +4207,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E158">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4231,21 +4231,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E159">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4255,21 +4255,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E160">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4279,21 +4279,21 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E161">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4303,21 +4303,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E162">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4327,21 +4327,21 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E163">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4351,21 +4351,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E164">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4375,21 +4375,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
         </is>
       </c>
       <c r="E165">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4399,21 +4399,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
+          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
+          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
         </is>
       </c>
       <c r="E166">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4423,21 +4423,21 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
+          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
+          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
         </is>
       </c>
       <c r="E167">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4447,21 +4447,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
+          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
+          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
         </is>
       </c>
       <c r="E168">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4471,21 +4471,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E169">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4495,21 +4495,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E170">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4519,21 +4519,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E171">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4543,21 +4543,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E172">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4567,21 +4567,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E173">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4591,21 +4591,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E174">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4615,21 +4615,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
         </is>
       </c>
       <c r="E175">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4639,21 +4639,21 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
+          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
+          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E176">
-        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4663,21 +4663,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
+          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
+          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E177">
-        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4687,21 +4687,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
+          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
         </is>
       </c>
       <c r="E178">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4711,21 +4711,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
+          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
         </is>
       </c>
       <c r="E179">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4940,10 +4940,9 @@
           <t>Tue, 07 Jul 2026 16:54:00 +0900</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+      <c r="E188">
+        <f>HYPERLINK("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg", IMAGE("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="189">

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -486,21 +486,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>** 전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
+          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
+          <t>https://sjbnews.com/news/news.php?number=884391</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
+          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -510,21 +510,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
+          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=884391</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
+          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -534,21 +534,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
+          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
+          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -558,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
+          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
+          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
+          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -606,21 +606,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
+          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
+          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
+          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
+          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
+          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
+          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
+          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
+          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
+          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
+          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
+          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
+          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
+          <t>** 전북대, 한화·현대로템·보잉 등 임원 객원교수 초빙…방산 인재양성 ...</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
+          <t>https://www.betanews.net/article/view/beta202607300039</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>** 전북대, 한화·현대로템·보잉 등 임원 객원교수 초빙…방산 인재양성 ...</t>
+          <t>K방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607300039</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:10:00 +0900</t>
+          <t>Tue, 15 Sep 2026 16:40:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>K-방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
+          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 16:40:00 +0900</t>
+          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
+          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
+          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
+          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
+          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -942,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
+          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
+          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -966,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
+          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
+          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -990,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
+          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
+          <t>https://sjbnews.com/news/news.php?number=887083</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
+          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1014,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
+          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=887083</t>
+          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
+          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1038,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
+          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1062,21 +1062,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
+          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1086,21 +1086,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
+          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
+          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1110,21 +1110,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
+          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
+          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
+          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1134,21 +1134,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
+          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1158,22 +1158,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
+          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
-        </is>
-      </c>
-      <c r="E31">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1182,23 +1183,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
+          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E32">
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1207,21 +1207,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
+          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
+          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
+          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
+          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
+          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1255,21 +1255,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
+          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
+          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1279,21 +1279,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
+          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
+          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
+          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1303,21 +1303,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
+          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
+          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
+          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1327,21 +1327,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
+          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
+          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1351,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
+          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
         <v/>
       </c>
     </row>
@@ -1375,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
+          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
+          <t>https://hbnpress.com/news/view/1065597442480538</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
+        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
+          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://hbnpress.com/news/view/1065597442480538</t>
+          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
+          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
+          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
+        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
+          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
+          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
+          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1495,21 +1495,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
+          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
+          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
+          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1543,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
+          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
+          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1567,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
+          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
+          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
         <v/>
       </c>
     </row>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
+          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1615,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
+          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
+          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
         <v/>
       </c>
     </row>
@@ -1639,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
+          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
+          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1663,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
+          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
+          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1687,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
+          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
+          <t>https://www.ajunews.com/view/20260908164442351</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
+          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1711,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
+          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
+          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
+          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1735,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
+          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
+          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1759,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
+          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
+          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
+          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1807,21 +1807,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
+          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260819500013</t>
+          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
+          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260916033541", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260916033541"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1855,21 +1855,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
+          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
+          <t>https://www.viva100.com/article/20260817500461</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
+          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260917033351", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260917033351"))</f>
         <v/>
       </c>
     </row>
@@ -1879,21 +1879,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
+          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260908164442351</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
+          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1903,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
+          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
+          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1927,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
+          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
+          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1951,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
+          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
+          <t>https://www.ajunews.com/view/20260806162915186</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
+          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1975,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
+          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260817500461</t>
+          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
+          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260916033608", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260916033608"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
+          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2023,21 +2023,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
+          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
+          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
+          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2047,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
+          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
+          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260806162915186</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2095,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
+          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
+          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2143,21 +2143,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
+          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
+          <t>https://www.betanews.net/article/view/beta202607290020</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
+          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2167,21 +2167,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
+          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
+          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
+          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2191,21 +2191,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
+          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2215,21 +2215,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
+          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
+          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2239,21 +2239,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
+          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2263,21 +2263,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
+          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607290020</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2287,21 +2287,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
+          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
+          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2311,21 +2311,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
+          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
+          <t>https://www.viva100.com/article/20260819500013</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260917033521", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260917033521"))</f>
         <v/>
       </c>
     </row>
@@ -2335,21 +2335,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
+          <t>전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
+          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2359,21 +2359,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
+          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
+          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2383,21 +2383,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
+          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
+          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2407,21 +2407,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
+          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
+          <t>https://www.viva100.com/article/20260812500685</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
+          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260917033538", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260917033538"))</f>
         <v/>
       </c>
     </row>
@@ -2431,21 +2431,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
+          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2455,21 +2455,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
+          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2479,21 +2479,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
+          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260812500685</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
+          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260916033734", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260916033734"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
         <v/>
       </c>
     </row>
@@ -2503,21 +2503,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
+          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
+          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2527,21 +2527,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
+          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
+          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2551,21 +2551,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
+          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
+          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2575,21 +2575,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
+          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2599,21 +2599,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
+          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2623,21 +2623,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
+          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
+          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
+          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2647,21 +2647,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
+          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
+          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
+          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2671,21 +2671,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
+          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
+          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
         <v/>
       </c>
     </row>
@@ -2695,21 +2695,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
+          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
+          <t>https://www.viva100.com/article/20260726500503</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
+          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260917033618", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260917033618"))</f>
         <v/>
       </c>
     </row>
@@ -2719,21 +2719,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
+          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2743,21 +2743,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
+          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2767,21 +2767,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
+          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260726500503</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
+          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260916033810", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260916033810"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2791,21 +2791,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
+          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
+          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2815,21 +2815,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
+          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
+          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2839,21 +2839,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
+          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
+          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2863,21 +2863,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
+          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
+          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2887,21 +2887,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
+          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
+          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
+          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
+        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2911,21 +2911,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
+          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
+          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2935,21 +2935,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
+          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
+          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2959,21 +2959,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
+          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
+          <t>https://www.ajunews.com/view/20260714135200349</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
+          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
         <v/>
       </c>
     </row>
@@ -2983,21 +2983,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
+          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
+          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
+          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3007,21 +3007,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
+          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
+          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3031,21 +3031,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
+          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260714135200349</t>
+          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
+          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3055,21 +3055,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
+          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
+          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3079,21 +3079,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
+          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
+          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3103,21 +3103,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
+          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
+          <t>https://www.viva100.com/article/20260712500414</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
+          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260917033704", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260917033704"))</f>
         <v/>
       </c>
     </row>
@@ -3127,21 +3127,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
+          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
+          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3151,21 +3151,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
+          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
+          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3175,21 +3175,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
+          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260712500414</t>
+          <t>https://www.news2day.co.kr/article/20260709500128</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
+          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260916033900", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260916033900"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
         <v/>
       </c>
     </row>
@@ -3199,21 +3199,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
+          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
+          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
+          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3223,21 +3223,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
+          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
+          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3247,21 +3247,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
+          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260709500128</t>
+          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3271,21 +3271,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
+          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
+          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3295,21 +3295,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
+          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3319,21 +3319,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
+          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3343,21 +3343,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
+          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
+          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3367,21 +3367,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
+          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3391,21 +3391,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
+          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
+          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3415,21 +3415,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
+          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
+          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
+          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3439,21 +3439,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
+          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
+          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3463,21 +3463,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3487,21 +3487,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3511,21 +3511,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
+          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
+          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3535,21 +3535,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3559,21 +3559,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3583,21 +3583,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
+          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
+          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3607,21 +3607,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
+          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
+          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3631,21 +3631,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
+          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
+          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3655,21 +3655,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
+          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
+          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
+          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3679,21 +3679,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
+          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
+          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -3703,21 +3703,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
+          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
+          <t>https://www.jjan.kr/article/20260614500064</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
+          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3727,21 +3727,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
+          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
+          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3751,21 +3751,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3775,21 +3775,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://www.jjan.kr/article/20260614500064</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3799,21 +3799,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3823,21 +3823,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3847,21 +3847,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3871,21 +3871,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3895,21 +3895,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3919,21 +3919,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3943,21 +3943,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>추미애, 핵심 공약 직접 챙긴다</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Fri, 01 May 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3967,21 +3967,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3991,21 +3991,21 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E149">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4015,21 +4015,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>추미애, 핵심 공약 직접 챙긴다</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 17:08:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E150">
-        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4039,21 +4039,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E151">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4063,21 +4063,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E152">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4087,21 +4087,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
         </is>
       </c>
       <c r="E153">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4111,21 +4111,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E154">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4135,21 +4135,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E155">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4159,21 +4159,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E156">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4183,21 +4183,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E157">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4207,21 +4207,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E158">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4231,21 +4231,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E159">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4255,21 +4255,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E160">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4279,21 +4279,21 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E161">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4303,21 +4303,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
         </is>
       </c>
       <c r="E162">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4327,21 +4327,21 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
         </is>
       </c>
       <c r="E163">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4351,21 +4351,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
         </is>
       </c>
       <c r="E164">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4375,21 +4375,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
+          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
+          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
         </is>
       </c>
       <c r="E165">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4399,21 +4399,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E166">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4423,21 +4423,21 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E167">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4447,21 +4447,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E168">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4471,21 +4471,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E169">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4495,21 +4495,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E170">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4519,21 +4519,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E171">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4543,21 +4543,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
         </is>
       </c>
       <c r="E172">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4567,21 +4567,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
         </is>
       </c>
       <c r="E173">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4591,21 +4591,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
         </is>
       </c>
       <c r="E174">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E190"/>
+  <dimension ref="A1:E194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>K방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
+          <t>첨단 드론 잇단 추락…방산 ‘무인 경쟁력’ 우려 확대</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1314054&amp;inflow=N</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 16:40:00 +0900</t>
+          <t>Thu, 17 Sep 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609171520", IMAGE("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609171520"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
+          <t>&amp;quot;민주당 맹목적 지지 벗어나 전북발전 성과 요구하자&amp;quot;…오창환 전북대 ...</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002457143?sid=102</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
+          <t>Thu, 17 Sep 2026 11:00:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
+          <t>K방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
+          <t>Tue, 15 Sep 2026 16:40:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -870,22 +870,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
+          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
-        </is>
-      </c>
-      <c r="E19">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
-        <v/>
+          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -894,21 +895,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
+          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -918,22 +919,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
+          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
-        </is>
-      </c>
-      <c r="E21">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
-        <v/>
+          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -942,21 +944,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
+          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -966,22 +968,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
+          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E23">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
-        <v/>
+          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -990,21 +993,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
+          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=887083</t>
+          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
+          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1014,21 +1017,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
+          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
+          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1038,21 +1041,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
+          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
+          <t>https://sjbnews.com/news/news.php?number=887083</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
+          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1062,21 +1065,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
+          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
+          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1086,21 +1089,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
+          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1110,21 +1113,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
+          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1134,21 +1137,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
+          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1158,23 +1161,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
+          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
+          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+        </is>
+      </c>
+      <c r="E31">
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1183,21 +1185,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
+          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
+          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1207,22 +1209,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
+          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E33">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
-        <v/>
+          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1231,21 +1234,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
+          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
+          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1255,21 +1258,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
+          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
+          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1279,21 +1282,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
+          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
+          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1303,21 +1306,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
+          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
+          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1327,21 +1330,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
+          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
+          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
+          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
+        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1351,21 +1354,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
+          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
+          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
+          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
+        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1375,21 +1378,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
+          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://hbnpress.com/news/view/1065597442480538</t>
+          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1402,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
+          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1426,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
+          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
+          <t>https://hbnpress.com/news/view/1065597442480538</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
+        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1450,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
+          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
+          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1474,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
+          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
+          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1495,21 +1498,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
+          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
+          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1522,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
+          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1543,21 +1546,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
+          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1567,21 +1570,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
+          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
+          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
+        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1591,21 +1594,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
+          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
+          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1615,21 +1618,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
+          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
+          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
         <v/>
       </c>
     </row>
@@ -1639,21 +1642,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
+          <t>전북대 이근회 석사과정생 차세대 RF 결합기 설계로 우수논문상.. '적은...</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=628473</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
+          <t>Thu, 17 Sep 2026 14:36:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1869,7 +1872,7 @@
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260917033351", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260917033351"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260918034155", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260918034155"))</f>
         <v/>
       </c>
     </row>
@@ -2311,21 +2314,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
+          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260819500013</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260917033521", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260917033521"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2335,21 +2338,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
+          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
+          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
         <v/>
       </c>
     </row>
@@ -2359,21 +2362,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
+          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
+          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2383,21 +2386,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
+          <t>'방산기업 미래 전략은?' 3회 전북 방위산업 육성 세미나</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014139089?sid=102</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
+          <t>Thu, 20 Aug 2026 17:02:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2407,21 +2410,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
+          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260812500685</t>
+          <t>https://www.viva100.com/article/20260819500013</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260917033538", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260917033538"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260918034259", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260918034259"))</f>
         <v/>
       </c>
     </row>
@@ -2431,21 +2434,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
+          <t>전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
+          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2455,21 +2458,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
+          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
+          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2479,21 +2482,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
+          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
+          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2503,21 +2506,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
+          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
+          <t>https://www.viva100.com/article/20260812500685</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
+          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260918034312", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260918034312"))</f>
         <v/>
       </c>
     </row>
@@ -2527,21 +2530,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
+          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2551,21 +2554,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
+          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2575,21 +2578,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
+          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
+          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
         <v/>
       </c>
     </row>
@@ -2599,21 +2602,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
+          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
+          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2623,21 +2626,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
+          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
+          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2647,21 +2650,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
+          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
+          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2671,21 +2674,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
+          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2695,21 +2698,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
+          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260726500503</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260917033618", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260917033618"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2719,21 +2722,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
+          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
+          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2743,21 +2746,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
+          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
+          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2767,21 +2770,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
+          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
+          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
         <v/>
       </c>
     </row>
@@ -2791,21 +2794,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
+          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
+          <t>https://www.viva100.com/article/20260726500503</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
+          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260918034340", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260918034340"))</f>
         <v/>
       </c>
     </row>
@@ -2815,21 +2818,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
+          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2839,21 +2842,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
+          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2863,21 +2866,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
+          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
+          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2887,21 +2890,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
+          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
+          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2911,21 +2914,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
+          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
+          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2935,21 +2938,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
+          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
+          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2959,21 +2962,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
+          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260714135200349</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
+          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2983,21 +2986,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
+          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
+          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
+          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
+        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3007,21 +3010,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
+          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
+          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3031,21 +3034,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
+          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
+          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3055,21 +3058,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
+          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
+          <t>https://www.ajunews.com/view/20260714135200349</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
+          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
         <v/>
       </c>
     </row>
@@ -3079,21 +3082,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
+          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
+          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
+          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3103,21 +3106,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
+          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260712500414</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
+          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260917033704", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260917033704"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3127,21 +3130,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
+          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
+          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
+          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3151,21 +3154,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
+          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
+          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3175,21 +3178,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
+          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260709500128</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
+          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3199,21 +3202,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
+          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
+          <t>https://www.viva100.com/article/20260712500414</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
+          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260918034414", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260918034414"))</f>
         <v/>
       </c>
     </row>
@@ -3223,22 +3226,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
+          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
-        </is>
-      </c>
-      <c r="E117">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
-        <v/>
+          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -3247,21 +3251,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
+          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
+          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3271,21 +3275,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
+          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
+          <t>https://www.news2day.co.kr/article/20260709500128</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
+          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
         <v/>
       </c>
     </row>
@@ -3295,21 +3299,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
+          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
+          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3319,21 +3323,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
+          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3343,21 +3347,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
+          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
+          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3367,21 +3371,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
+          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
+          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3391,21 +3395,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
+          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3415,21 +3419,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
+          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3439,21 +3443,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
+          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
+          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3463,21 +3467,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3487,21 +3491,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3511,21 +3515,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
+          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
+          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
+          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3535,21 +3539,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
+          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
+          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3559,21 +3563,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3583,21 +3587,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3607,21 +3611,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
+          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
+          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3631,21 +3635,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
+          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
+          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3655,21 +3659,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
+          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
+          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3679,21 +3683,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
+          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
+          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3703,21 +3707,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
+          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.jjan.kr/article/20260614500064</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
+          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3727,21 +3731,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
+          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
+          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3751,21 +3755,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3775,21 +3779,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -3799,21 +3803,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://www.jjan.kr/article/20260614500064</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3823,21 +3827,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3847,21 +3851,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3871,21 +3875,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3895,22 +3899,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E145">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
-        <v/>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -3919,21 +3924,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3943,21 +3948,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>추미애, 핵심 공약 직접 챙긴다</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 17:08:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3967,21 +3972,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3991,21 +3996,21 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E149">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4015,21 +4020,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E150">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4039,21 +4044,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>추미애, 핵심 공약 직접 챙긴다</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Fri, 01 May 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E151">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4063,21 +4068,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E152">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4087,21 +4092,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E153">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4111,21 +4116,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E154">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4135,21 +4140,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E155">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4159,21 +4164,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E156">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4183,21 +4188,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
         </is>
       </c>
       <c r="E157">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4207,21 +4212,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E158">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4231,21 +4236,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E159">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4255,21 +4260,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E160">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4279,21 +4284,21 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E161">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4303,21 +4308,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E162">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4327,22 +4332,23 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E163">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
-        <v/>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -4351,21 +4357,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E164">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4375,21 +4381,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E165">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4399,21 +4405,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
         </is>
       </c>
       <c r="E166">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4423,21 +4429,21 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
         </is>
       </c>
       <c r="E167">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4447,21 +4453,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
         </is>
       </c>
       <c r="E168">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4471,21 +4477,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
         </is>
       </c>
       <c r="E169">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4495,21 +4501,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E170">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4519,21 +4525,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E171">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4543,21 +4549,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E172">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4567,21 +4573,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E173">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4591,21 +4597,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E174">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4615,21 +4621,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E175">
-        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4639,21 +4645,21 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
+          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
         </is>
       </c>
       <c r="E176">
-        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4663,21 +4669,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
+          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
+          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
         </is>
       </c>
       <c r="E177">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4687,21 +4693,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
+          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
+          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
         </is>
       </c>
       <c r="E178">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4711,21 +4717,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
+          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
+          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
+          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
         </is>
       </c>
       <c r="E179">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4735,21 +4741,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
+          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
+          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E180">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4759,21 +4765,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
+          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2605457</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
+          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E181">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4783,21 +4789,21 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
+          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
         </is>
       </c>
       <c r="E182">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4807,21 +4813,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
+          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
+          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
         </is>
       </c>
       <c r="E183">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4831,21 +4837,21 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
+          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
+          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
         </is>
       </c>
       <c r="E184">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4855,21 +4861,21 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
+          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
+          <t>https://www.etoday.co.kr/news/view/2605457</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
+          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
         </is>
       </c>
       <c r="E185">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
         <v/>
       </c>
     </row>
@@ -4879,21 +4885,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
+          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
+          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E186">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4903,21 +4909,21 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>성능보다 우선한 '동맹'…캐나다, 왜 독일 선택했나?</t>
+          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000625036?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 21:20:00 +0900</t>
+          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
         </is>
       </c>
       <c r="E187">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4927,21 +4933,21 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>나토 국방비 증액에도 생산 병목…기회 잡는 K-방산</t>
+          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>http://www.metroseoul.co.kr/article/20260707500477</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:54:00 +0900</t>
+          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
         </is>
       </c>
       <c r="E188">
-        <f>HYPERLINK("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg", IMAGE("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4951,21 +4957,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
+          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
+          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E189">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4975,20 +4981,116 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
+        </is>
+      </c>
+      <c r="E190">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>성능보다 우선한 '동맹'…캐나다, 왜 독일 선택했나?</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/448/0000625036?sid=101</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 21:20:00 +0900</t>
+        </is>
+      </c>
+      <c r="E191">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>나토 국방비 증액에도 생산 병목…기회 잡는 K-방산</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>http://www.metroseoul.co.kr/article/20260707500477</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 16:54:00 +0900</t>
+        </is>
+      </c>
+      <c r="E192">
+        <f>HYPERLINK("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg", IMAGE("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
+        </is>
+      </c>
+      <c r="E193">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
           <t>[본지-대교협 공동기획中] 생성형 AI 기반 수업 혁신 확산 속 &amp;quot;인간 고유...</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="C194" t="inlineStr">
         <is>
           <t>https://news.unn.net/news/articleView.html?idxno=593399</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 09:00:00 +0900</t>
         </is>
       </c>
-      <c r="E190">
+      <c r="E194">
         <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg"))</f>
         <v/>
       </c>
@@ -5004,7 +5106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5136,21 +5238,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>** [2026방산포럼] '한·UAE' 방산 협력 넓힌다···AI부터 KF-21까지 협력...</t>
+          <t>** K방산 수출, 이제는 정보다 [기고]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2444556</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thu, 02 Jul 2026 03:51:00 +0900</t>
+          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2444556_1281841_516_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2444556_1281841_516_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5160,21 +5262,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>** K방산 수출, 이제는 정보다 [기고]</t>
+          <t>** 포티투마루, ‘글로벌 디지털 포럼’에서 K-팔란티어 육성 전략 제시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
+          <t>https://www.etoday.co.kr/news/view/2605499</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
+          <t>Tue, 21 Jul 2026 09:18:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png"))</f>
         <v/>
       </c>
     </row>
@@ -5184,44 +5286,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>** 포티투마루, ‘글로벌 디지털 포럼’에서 K-팔란티어 육성 전략 제시</t>
+          <t>** [알립니다] 제2회 국방방산전략포럼 개최합니다</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2605499</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004602094?sid=100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 21 Jul 2026 09:18:00 +0900</t>
+          <t>Sun, 22 Mar 2026 20:46:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>** [알립니다] 제2회 국방방산전략포럼 개최합니다</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004602094?sid=100</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sun, 22 Mar 2026 20:46:00 +0900</t>
-        </is>
-      </c>
-      <c r="E9">
         <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/22/0004602094_001_20260323095513484.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/22/0004602094_001_20260323095513484.jpg?type=w800"))</f>
         <v/>
       </c>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -462,21 +462,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>** 전북대학교 계약정원제 사업, 우주항공·AI·첨단방산 미래인재 양성 '비...</t>
+          <t>** 전북대, 방산기업 15곳과 '교육부터 채용까지'</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=210469</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004191066?sid=102</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sat, 12 Sep 2026 16:34:00 +0900</t>
+          <t>Fri, 18 Sep 2026 16:55:00 +0900</t>
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/09/18/0004191066_001_20260918165510107.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/09/18/0004191066_001_20260918165510107.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -486,21 +486,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
+          <t>** 전북대, KAI·현대로템 등 15개사와 '방산 인재 채용 직행로' 연다</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=884391</t>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1569395</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
+          <t>Fri, 18 Sep 2026 15:56:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
+        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202609/1569395_784381_4028_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202609/1569395_784381_4028_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -510,21 +510,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
+          <t>** 전북대, 방산기업 15곳과 '인재 육성 채용연계 산학협력 모델' 본격 가동</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003468198?sid=102</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
+          <t>Fri, 18 Sep 2026 10:49:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/18/0003468198_001_20260918104913691.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/18/0003468198_001_20260918104913691.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -534,21 +534,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
+          <t>** 전북대학교 계약정원제 사업, 우주항공·AI·첨단방산 미래인재 양성 '비...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=210469</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
+          <t>Sat, 12 Sep 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -558,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
+          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
+          <t>https://sjbnews.com/news/news.php?number=884391</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
+          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
+          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
+          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -606,21 +606,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
+          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
+          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
+          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
+          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
+          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
+          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
+          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
+          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
+          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
+          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
+          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>** 전북대, 한화·현대로템·보잉 등 임원 객원교수 초빙…방산 인재양성 ...</t>
+          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607300039</t>
+          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:10:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg"))</f>
+        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>첨단 드론 잇단 추락…방산 ‘무인 경쟁력’ 우려 확대</t>
+          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1314054&amp;inflow=N</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 15:00:00 +0900</t>
+          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609171520", IMAGE("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609171520"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>&amp;quot;민주당 맹목적 지지 벗어나 전북발전 성과 요구하자&amp;quot;…오창환 전북대 ...</t>
+          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002457143?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 11:00:00 +0900</t>
+          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>K방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
+          <t>** 전북대, 한화·현대로템·보잉 등 임원 객원교수 초빙…방산 인재양성 ...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
+          <t>https://www.betanews.net/article/view/beta202607300039</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 16:40:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -870,23 +870,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
+          <t>전북대, 방산기업 15곳과 맞춤형 인재양성 프로그램 운영</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014200391?sid=102</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 18 Sep 2026 16:41:00 +0900</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -895,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
+          <t>첨단 드론 잇단 추락…방산 ‘무인 경쟁력’ 우려 확대</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1314054&amp;inflow=N</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
+          <t>Thu, 17 Sep 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945", IMAGE("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945"))</f>
         <v/>
       </c>
     </row>
@@ -919,23 +918,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
+          <t>&amp;quot;민주당 맹목적 지지 벗어나 전북발전 성과 요구하자&amp;quot;…오창환 전북대 ...</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002457143?sid=102</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 17 Sep 2026 11:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E21">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -944,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
+          <t>K방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
+          <t>Tue, 15 Sep 2026 16:40:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -968,23 +966,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
+          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="E23">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -993,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
+          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1017,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
+          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1041,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
+          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=887083</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1065,21 +1062,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
+          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1089,21 +1086,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
+          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
+          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1113,21 +1110,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
+          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
+          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1137,21 +1134,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
+          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
+          <t>https://sjbnews.com/news/news.php?number=887083</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
+          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1161,21 +1158,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
+          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1185,21 +1182,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
+          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1209,23 +1206,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
+          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E33">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1234,21 +1230,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
+          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
+          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1258,21 +1254,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
+          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
+          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1282,21 +1278,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
+          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
+          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1306,22 +1302,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
+          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
-        </is>
-      </c>
-      <c r="E37">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
-        <v/>
+          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1330,21 +1327,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
+          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
+          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
         </is>
       </c>
       <c r="E38">
-        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1354,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
+          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
+          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
+          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1378,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
+          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
+          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1402,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
+          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
+          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1426,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
+          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://hbnpress.com/news/view/1065597442480538</t>
+          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
+          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
+        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1450,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
+          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
+          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
+          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1474,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
+          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
+          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1498,21 +1495,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
+          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
         <v/>
       </c>
     </row>
@@ -1522,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
+          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
+          <t>https://hbnpress.com/news/view/1065597442480538</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
+        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1546,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
+          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
+          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1570,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
+          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
+          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
+        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1594,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
+          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
+          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1618,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
+          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1642,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>전북대 이근회 석사과정생 차세대 RF 결합기 설계로 우수논문상.. '적은...</t>
+          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=628473</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 14:36:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1666,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
+          <t>전북대 이근회 석사과정생 차세대 RF 결합기 설계로 우수논문상.. '적은...</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=628473</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
+          <t>Thu, 17 Sep 2026 14:36:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1690,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
+          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260908164442351</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
+          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1714,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
+          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
+          <t>https://www.ajunews.com/view/20260908164442351</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
+          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1738,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
+          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
+          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
+          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1762,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
+          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
+          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1786,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
+          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
+          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1810,21 +1807,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
+          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
+          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1834,21 +1831,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
+          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
+          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1858,21 +1855,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
+          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260817500461</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260918034155", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260918034155"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1882,21 +1879,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
+          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1906,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
+          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1930,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
+          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
+          <t>https://www.viva100.com/article/20260817500461</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
+          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260919025853", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260919025853"))</f>
         <v/>
       </c>
     </row>
@@ -1954,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
+          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260806162915186</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
+          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1978,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
+          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
+          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2002,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
+          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
+          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
+          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2026,21 +2023,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
+          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
+          <t>https://www.ajunews.com/view/20260806162915186</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2050,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
+          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
+          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
+          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2074,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
+          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2098,21 +2095,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
+          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
+          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
+          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2122,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
+          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2146,21 +2143,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
+          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607290020</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2170,21 +2167,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
+          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -2194,21 +2191,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
+          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2218,21 +2215,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
+          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
+          <t>https://www.betanews.net/article/view/beta202607290020</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
+          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2242,21 +2239,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
+          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
+          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2266,21 +2263,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
+          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2290,21 +2287,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
+          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2314,21 +2311,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
+          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
+          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2338,21 +2335,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
+          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
+          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2362,21 +2359,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
+          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
+          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2386,21 +2383,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>'방산기업 미래 전략은?' 3회 전북 방위산업 육성 세미나</t>
+          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014139089?sid=102</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:02:00 +0900</t>
+          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
         <v/>
       </c>
     </row>
@@ -2410,21 +2407,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
+          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260819500013</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260918034259", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260918034259"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2434,21 +2431,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
+          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
+          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
         <v/>
       </c>
     </row>
@@ -2458,21 +2455,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
+          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
+          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2482,21 +2479,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
+          <t>'방산기업 미래 전략은?' 3회 전북 방위산업 육성 세미나</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014139089?sid=102</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
+          <t>Thu, 20 Aug 2026 17:02:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2506,21 +2503,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
+          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260812500685</t>
+          <t>https://www.viva100.com/article/20260819500013</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260918034312", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260918034312"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260919030039", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260919030039"))</f>
         <v/>
       </c>
     </row>
@@ -2530,21 +2527,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
+          <t>전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
+          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2554,21 +2551,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
+          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
+          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2578,21 +2575,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
+          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
+          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2602,21 +2599,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
+          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
+          <t>https://www.viva100.com/article/20260812500685</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
+          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260919030055", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260919030055"))</f>
         <v/>
       </c>
     </row>
@@ -2626,21 +2623,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
+          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2650,21 +2647,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
+          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2674,21 +2671,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
+          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
+          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
         <v/>
       </c>
     </row>
@@ -2698,21 +2695,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
+          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
+          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2722,21 +2719,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
+          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
+          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2746,21 +2743,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
+          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
+          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2770,21 +2767,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
+          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2794,21 +2791,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
+          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260726500503</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260918034340", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260918034340"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2818,21 +2815,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
+          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
+          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2842,21 +2839,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
+          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
+          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2866,21 +2863,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
+          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
+          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
         <v/>
       </c>
     </row>
@@ -2890,21 +2887,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
+          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
+          <t>https://www.viva100.com/article/20260726500503</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
+          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260919030136", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260919030136"))</f>
         <v/>
       </c>
     </row>
@@ -2914,21 +2911,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
+          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2938,21 +2935,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
+          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2962,21 +2959,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
+          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
+          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2986,21 +2983,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
+          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
+          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3010,21 +3007,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
+          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
+          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3034,21 +3031,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
+          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
+          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3058,21 +3055,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
+          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260714135200349</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
+          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3082,21 +3079,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
+          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
+          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
+          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
+        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3106,21 +3103,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
+          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
+          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3130,21 +3127,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
+          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
+          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3154,21 +3151,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
+          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
+          <t>https://www.ajunews.com/view/20260714135200349</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
+          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
         <v/>
       </c>
     </row>
@@ -3178,21 +3175,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
+          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
+          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
+          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3202,21 +3199,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
+          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260712500414</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
+          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260918034414", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260918034414"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3226,23 +3223,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
+          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
+          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E117">
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -3251,21 +3247,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
+          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
+          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3275,21 +3271,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
+          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260709500128</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
+          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3299,21 +3295,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
+          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
+          <t>https://www.viva100.com/article/20260712500414</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
+          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260919030226", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260919030226"))</f>
         <v/>
       </c>
     </row>
@@ -3323,21 +3319,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
+          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E121">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3347,21 +3343,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
+          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
+          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3371,21 +3367,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
+          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
+          <t>https://www.news2day.co.kr/article/20260709500128</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
+          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
         <v/>
       </c>
     </row>
@@ -3395,21 +3391,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
+          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
+          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3419,21 +3415,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
+          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3443,21 +3439,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>한화오션, 60조 캐나다 잠수함 고배…이 대통령, 'K-방산 세일즈' 돌파구</t>
+          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>http://mbnmoney.mbn.co.kr/news/view?news_no=MM1005874272</t>
+          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:36:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg", IMAGE("https://imgmm.mbn.co.kr/vod/news/103/2026/07/07/20260707163441_10_103_0_MM1005874272_4_116.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3467,21 +3463,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>팀코리아, 캐나다 잠수함 수주 좌초...유럽 방산 진출 '적신호'</t>
+          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=249725</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:22:00 +0900</t>
+          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/249725_259957_321_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3491,21 +3487,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>캐나다 잠수함 고배 'K-방산'…&amp;quot;'MOU·협정' 나토 심장 노려야&amp;quot;</t>
+          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005382538?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 13:45:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/07/0005382538_001_20260707134911770.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3515,21 +3511,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2년 표류 끝 사업 재개…7.8조원 KDDX가 남긴 과제, &amp;quot;갈등보다 국익 우선...</t>
+          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/138/0002233138?sid=101</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sat, 04 Jul 2026 15:25:00 +0900</t>
+          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/138/2026/07/04/0002233138_001_20260704152809051.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3539,21 +3535,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3563,12 +3559,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3577,7 +3573,7 @@
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3587,21 +3583,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3611,21 +3607,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
+          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
+          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3635,21 +3631,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
+          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
+          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3659,21 +3655,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
+          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
+          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3683,21 +3679,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
+          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
+          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3707,21 +3703,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
+          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
+          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3731,21 +3727,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
+          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
+          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
+          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3755,21 +3751,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
+          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
+          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -3779,21 +3775,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
+          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
+          <t>https://www.jjan.kr/article/20260614500064</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
+          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3803,21 +3799,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
+          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://www.jjan.kr/article/20260614500064</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
+          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3827,21 +3823,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3851,21 +3847,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3875,21 +3871,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3899,23 +3895,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+        </is>
+      </c>
+      <c r="E145">
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="146">
@@ -3924,21 +3919,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3948,21 +3943,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3972,21 +3967,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3996,21 +3991,21 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E149">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4020,21 +4015,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>추미애, 핵심 공약 직접 챙긴다</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Fri, 01 May 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E150">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4044,21 +4039,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>추미애, 핵심 공약 직접 챙긴다</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 17:08:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E151">
-        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4068,21 +4063,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E152">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4092,21 +4087,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E153">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4116,21 +4111,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E154">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4140,21 +4135,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E155">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4164,21 +4159,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
         </is>
       </c>
       <c r="E156">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4188,21 +4183,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E157">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4212,21 +4207,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E158">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4236,21 +4231,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E159">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4260,21 +4255,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E160">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4284,21 +4279,21 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E161">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4308,21 +4303,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E162">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4332,23 +4327,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+        </is>
+      </c>
+      <c r="E163">
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -4357,21 +4351,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E164">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4381,21 +4375,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
         </is>
       </c>
       <c r="E165">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4405,21 +4399,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
+          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
+          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
         </is>
       </c>
       <c r="E166">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4429,21 +4423,21 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
+          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
+          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
         </is>
       </c>
       <c r="E167">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4453,21 +4447,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
+          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
+          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
         </is>
       </c>
       <c r="E168">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4477,21 +4471,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E169">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4501,21 +4495,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E170">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4525,21 +4519,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E171">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4549,21 +4543,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E172">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4573,21 +4567,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E173">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4597,21 +4591,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E174">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4621,21 +4615,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
         </is>
       </c>
       <c r="E175">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4645,21 +4639,21 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
+          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
+          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
         </is>
       </c>
       <c r="E176">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4669,21 +4663,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
+          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
+          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
         </is>
       </c>
       <c r="E177">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4693,21 +4687,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
+          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
+          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
+          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
         </is>
       </c>
       <c r="E178">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4717,21 +4711,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
+          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
+          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E179">
-        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4741,21 +4735,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
+          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
+          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E180">
-        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4765,21 +4759,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
+          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
         </is>
       </c>
       <c r="E181">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4789,21 +4783,21 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
+          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
         </is>
       </c>
       <c r="E182">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4813,21 +4807,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
+          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
+          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
         </is>
       </c>
       <c r="E183">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4837,21 +4831,21 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
+          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
+          <t>https://www.etoday.co.kr/news/view/2605457</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
+          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
         </is>
       </c>
       <c r="E184">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
         <v/>
       </c>
     </row>
@@ -4861,21 +4855,21 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
+          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2605457</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
+          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E185">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4885,21 +4879,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
+          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
+          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
         </is>
       </c>
       <c r="E186">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4909,21 +4903,21 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
+          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
+          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
         </is>
       </c>
       <c r="E187">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4933,21 +4927,21 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
+          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
+          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E188">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4957,21 +4951,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
+          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
+          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E189">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4981,21 +4975,21 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
+          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
         </is>
       </c>
       <c r="E190">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260919025853", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260919025853"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260920023519", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260920023519"))</f>
         <v/>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260919030039", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260919030039"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260920023650", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260920023650"))</f>
         <v/>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260919030055", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260919030055"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260920023705", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260920023705"))</f>
         <v/>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260919030136", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260919030136"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260920023739", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260920023739"))</f>
         <v/>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260919030226", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260919030226"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260920023816", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260920023816"))</f>
         <v/>
       </c>
     </row>
@@ -3332,9 +3332,10 @@
           <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
         </is>
       </c>
-      <c r="E121">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
-        <v/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -3535,12 +3536,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3549,7 +3550,7 @@
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3559,12 +3560,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3573,7 +3574,7 @@
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E194"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,21 +462,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>** 전북대, 방산기업 15곳과 '교육부터 채용까지'</t>
+          <t>** 전북대, 15곳 방산기업과 ‘교육부터 채용까지' 연계</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004191066?sid=102</t>
+          <t>https://sjbnews.com/news/news.php?number=888194</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 18 Sep 2026 16:55:00 +0900</t>
+          <t>Sun, 20 Sep 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/09/18/0004191066_001_20260918165510107.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/09/18/0004191066_001_20260918165510107.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_888194_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_888194_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -486,21 +486,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>** 전북대, KAI·현대로템 등 15개사와 '방산 인재 채용 직행로' 연다</t>
+          <t>** 전북대, 방산기업 15곳과 '교육부터 채용까지'</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>http://www.domin.co.kr/news/articleView.html?idxno=1569395</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004191066?sid=102</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fri, 18 Sep 2026 15:56:00 +0900</t>
+          <t>Fri, 18 Sep 2026 16:55:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202609/1569395_784381_4028_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202609/1569395_784381_4028_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/09/18/0004191066_001_20260918165510107.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/09/18/0004191066_001_20260918165510107.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -510,21 +510,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>** 전북대, 방산기업 15곳과 '인재 육성 채용연계 산학협력 모델' 본격 가동</t>
+          <t>** 전북대, KAI·현대로템 등 15개사와 '방산 인재 채용 직행로' 연다</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003468198?sid=102</t>
+          <t>http://www.domin.co.kr/news/articleView.html?idxno=1569395</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fri, 18 Sep 2026 10:49:00 +0900</t>
+          <t>Fri, 18 Sep 2026 15:56:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/18/0003468198_001_20260918104913691.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/18/0003468198_001_20260918104913691.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.domin.co.kr/news/thumbnail/202609/1569395_784381_4028_v150.jpg", IMAGE("http://www.domin.co.kr/news/thumbnail/202609/1569395_784381_4028_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -534,21 +534,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>** 전북대학교 계약정원제 사업, 우주항공·AI·첨단방산 미래인재 양성 '비...</t>
+          <t>** 전북대, 방산기업 15곳과 '인재 육성 채용연계 산학협력 모델' 본격 가동</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=210469</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003468198?sid=102</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sat, 12 Sep 2026 16:34:00 +0900</t>
+          <t>Fri, 18 Sep 2026 10:49:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/18/0003468198_001_20260918104913691.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/18/0003468198_001_20260918104913691.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -558,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
+          <t>** 전북대학교 계약정원제 사업, 우주항공·AI·첨단방산 미래인재 양성 '비...</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=884391</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=210469</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
+          <t>Sat, 12 Sep 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
+          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
+          <t>https://sjbnews.com/news/news.php?number=884391</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
+          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -606,21 +606,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
+          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
+          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
+          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
+          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
+          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
+          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
+          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
+          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
+          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
+          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
+          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
+          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
+          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
+          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
+          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
+          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
+          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>** 전북대, 한화·현대로템·보잉 등 임원 객원교수 초빙…방산 인재양성 ...</t>
+          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607300039</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:10:00 +0900</t>
+          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>전북대, 방산기업 15곳과 맞춤형 인재양성 프로그램 운영</t>
+          <t>** 전북대, 한화·현대로템·보잉 등 임원 객원교수 초빙…방산 인재양성 ...</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014200391?sid=102</t>
+          <t>https://www.betanews.net/article/view/beta202607300039</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 18 Sep 2026 16:41:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>첨단 드론 잇단 추락…방산 ‘무인 경쟁력’ 우려 확대</t>
+          <t>전북대, 방산기업 15곳과 맞춤형 인재양성 프로그램 운영</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1314054&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014200391?sid=102</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 15:00:00 +0900</t>
+          <t>Fri, 18 Sep 2026 16:41:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945", IMAGE("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>&amp;quot;민주당 맹목적 지지 벗어나 전북발전 성과 요구하자&amp;quot;…오창환 전북대 ...</t>
+          <t>첨단 드론 잇단 추락…방산 ‘무인 경쟁력’ 우려 확대</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002457143?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1314054&amp;inflow=N</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 11:00:00 +0900</t>
+          <t>Thu, 17 Sep 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945", IMAGE("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945"))</f>
         <v/>
       </c>
     </row>
@@ -942,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>K방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
+          <t>&amp;quot;민주당 맹목적 지지 벗어나 전북발전 성과 요구하자&amp;quot;…오창환 전북대 ...</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002457143?sid=102</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 16:40:00 +0900</t>
+          <t>Thu, 17 Sep 2026 11:00:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -966,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
+          <t>K방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
+          <t>Tue, 15 Sep 2026 16:40:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -990,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
+          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
+          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1014,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
+          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1038,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
+          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1062,21 +1062,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
+          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1086,21 +1086,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
+          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1110,21 +1110,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
+          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
+          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
+          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1134,21 +1134,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
+          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=887083</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
+          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1158,21 +1158,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
+          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
+          <t>https://sjbnews.com/news/news.php?number=887083</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
+          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1182,21 +1182,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
+          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
+          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1206,21 +1206,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
+          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1230,21 +1230,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
+          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1254,21 +1254,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
+          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1278,21 +1278,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
+          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1302,23 +1302,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
+          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+        </is>
+      </c>
+      <c r="E37">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -1327,22 +1326,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
+          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E38">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
-        <v/>
+          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1351,21 +1351,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
+          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
+          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
         </is>
       </c>
       <c r="E39">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1375,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
+          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
+          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
+          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
+          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
+          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
+          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
+          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
+          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
+          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
+          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
+          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
+          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1495,21 +1495,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
+          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
+          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
+        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
+          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://hbnpress.com/news/view/1065597442480538</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
         <v/>
       </c>
     </row>
@@ -1543,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
+          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
+          <t>https://hbnpress.com/news/view/1065597442480538</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
+        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1567,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
+          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
+          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
+          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
+          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1615,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
+          <t>전북대 이근회 석사과정생 차세대 RF 결합기 설계로 우수논문상.. '적은...</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=628473</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
+          <t>Thu, 17 Sep 2026 14:36:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1639,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
+          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
+          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1663,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>전북대 이근회 석사과정생 차세대 RF 결합기 설계로 우수논문상.. '적은...</t>
+          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=628473</t>
+          <t>https://www.ajunews.com/view/20260908164442351</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 14:36:00 +0900</t>
+          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1687,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
+          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
+          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
+          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1711,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
+          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260908164442351</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
+          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1735,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
+          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
+          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1759,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
+          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
+          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
+          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260920023519", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260920023519"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260921024743", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260921024743"))</f>
         <v/>
       </c>
     </row>
@@ -2335,21 +2335,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>모레, 전북대 피지컬 AI 기술이전…공간지능 플랫폼 개발 [로보 인사이...</t>
+          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004646314?sid=105</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 09:25:00 +0900</t>
+          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/07/29/0004646314_001_20260729092510287.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2359,21 +2359,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
+          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
+          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
         <v/>
       </c>
     </row>
@@ -2383,21 +2383,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
+          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2407,21 +2407,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
+          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
+          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
         <v/>
       </c>
     </row>
@@ -2431,21 +2431,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
+          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
+          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2455,21 +2455,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
+          <t>'방산기업 미래 전략은?' 3회 전북 방위산업 육성 세미나</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014139089?sid=102</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
+          <t>Thu, 20 Aug 2026 17:02:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2479,21 +2479,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>'방산기업 미래 전략은?' 3회 전북 방위산업 육성 세미나</t>
+          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014139089?sid=102</t>
+          <t>https://www.viva100.com/article/20260819500013</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:02:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260921024852", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260921024852"))</f>
         <v/>
       </c>
     </row>
@@ -2503,21 +2503,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
+          <t>전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260819500013</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
+          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260920023650", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260920023650"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2527,21 +2527,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
+          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
+          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2551,21 +2551,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
+          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
+          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2575,21 +2575,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
+          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
+          <t>https://www.viva100.com/article/20260812500685</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
+          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260921024904", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260921024904"))</f>
         <v/>
       </c>
     </row>
@@ -2599,21 +2599,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
+          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260812500685</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260920023705", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260920023705"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2623,21 +2623,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
+          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2647,21 +2647,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
+          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
+          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
         <v/>
       </c>
     </row>
@@ -2671,21 +2671,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
+          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
+          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2695,21 +2695,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
+          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
+          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2719,21 +2719,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
+          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
+          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2743,21 +2743,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
+          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2767,21 +2767,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
+          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2791,21 +2791,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
+          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
+          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2815,21 +2815,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
+          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
+          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2839,21 +2839,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
+          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
+          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
         <v/>
       </c>
     </row>
@@ -2863,21 +2863,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
+          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
+          <t>https://www.viva100.com/article/20260726500503</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
+          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260921024932", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260921024932"))</f>
         <v/>
       </c>
     </row>
@@ -2887,21 +2887,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
+          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260726500503</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260920023739", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260920023739"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2935,21 +2935,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
+          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
+          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2959,21 +2959,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
+          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
+          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2983,21 +2983,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
+          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
+          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3007,21 +3007,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
+          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
+          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3031,21 +3031,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
+          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
+          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3055,21 +3055,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
+          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
+          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
+          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
+        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3079,21 +3079,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
+          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
+          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3103,21 +3103,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
+          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
+          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3127,21 +3127,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
+          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
+          <t>https://www.ajunews.com/view/20260714135200349</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
+          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
         <v/>
       </c>
     </row>
@@ -3151,21 +3151,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
+          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260714135200349</t>
+          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
+          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
+        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3175,21 +3175,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
+          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
+          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3199,21 +3199,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
+          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
+          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3223,21 +3223,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
+          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
+          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3247,21 +3247,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
+          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
+          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3271,21 +3271,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
+          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
+          <t>https://www.viva100.com/article/20260712500414</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
+          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260921025009", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260921025009"))</f>
         <v/>
       </c>
     </row>
@@ -3295,21 +3295,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
+          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260712500414</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
+          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260920023816", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260920023816"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3319,23 +3319,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
+          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
+        </is>
+      </c>
+      <c r="E121">
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -3344,21 +3343,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
+          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
+          <t>https://www.news2day.co.kr/article/20260709500128</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
+          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
         <v/>
       </c>
     </row>
@@ -3368,21 +3367,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
+          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260709500128</t>
+          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
+          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3392,21 +3391,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
+          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3416,21 +3415,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
+          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
+          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3440,21 +3439,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
+          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
+          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3464,21 +3463,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
+          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
+          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3488,21 +3487,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3512,21 +3511,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3536,21 +3535,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3560,21 +3559,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3584,21 +3583,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
+          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
+          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3608,21 +3607,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
+          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
+          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3632,21 +3631,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
+          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
+          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3656,21 +3655,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
+          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
+          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3680,21 +3679,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
+          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
+          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
+          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3704,21 +3703,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
+          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
+          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -3728,21 +3727,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
+          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
+          <t>https://www.jjan.kr/article/20260614500064</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
+          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3752,21 +3751,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
+          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
+          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3776,21 +3775,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://www.jjan.kr/article/20260614500064</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3800,21 +3799,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3824,21 +3823,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3848,21 +3847,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3872,21 +3871,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3896,21 +3895,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3920,21 +3919,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3944,21 +3943,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3968,21 +3967,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>추미애, 핵심 공약 직접 챙긴다</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Fri, 01 May 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3992,21 +3991,21 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E149">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4016,21 +4015,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>추미애, 핵심 공약 직접 챙긴다</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 17:08:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E150">
-        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4040,21 +4039,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E151">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4064,21 +4063,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E152">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4088,21 +4087,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E153">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4112,21 +4111,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
         </is>
       </c>
       <c r="E154">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4136,21 +4135,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E155">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4160,21 +4159,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
+          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
+          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E156">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4184,21 +4183,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E157">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4208,21 +4207,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E158">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4232,21 +4231,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E159">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4256,21 +4255,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E160">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4280,21 +4279,21 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E161">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4304,21 +4303,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E162">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4328,21 +4327,21 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
         </is>
       </c>
       <c r="E163">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4352,21 +4351,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
         </is>
       </c>
       <c r="E164">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4376,21 +4375,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
+          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
+          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
         </is>
       </c>
       <c r="E165">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4400,21 +4399,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
+          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
+          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
         </is>
       </c>
       <c r="E166">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4424,21 +4423,21 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E167">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4448,21 +4447,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E168">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4472,21 +4471,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E169">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4496,21 +4495,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E170">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4520,21 +4519,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E171">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4544,21 +4543,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E172">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4568,21 +4567,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E173">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4592,21 +4591,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
         </is>
       </c>
       <c r="E174">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4616,21 +4615,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
+          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
+          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
         </is>
       </c>
       <c r="E175">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4640,21 +4639,21 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
+          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
+          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
         </is>
       </c>
       <c r="E176">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4664,21 +4663,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
+          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
+          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
+          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
         </is>
       </c>
       <c r="E177">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4688,21 +4687,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
+          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
+          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E178">
-        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4712,21 +4711,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
+          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
+          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E179">
-        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4736,21 +4735,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
+          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
         </is>
       </c>
       <c r="E180">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4760,21 +4759,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
+          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
         </is>
       </c>
       <c r="E181">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4784,21 +4783,21 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
+          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
+          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
         </is>
       </c>
       <c r="E182">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4808,21 +4807,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
+          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
+          <t>https://www.etoday.co.kr/news/view/2605457</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
+          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
         </is>
       </c>
       <c r="E183">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
         <v/>
       </c>
     </row>
@@ -4832,21 +4831,21 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
+          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2605457</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
+          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E184">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4856,21 +4855,21 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
+          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
+          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
         </is>
       </c>
       <c r="E185">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4880,21 +4879,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
+          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
+          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
         </is>
       </c>
       <c r="E186">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4904,21 +4903,21 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
+          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
+          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E187">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4928,21 +4927,21 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
+          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
+          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E188">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4952,21 +4951,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
+          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
         </is>
       </c>
       <c r="E189">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5024,21 +5023,21 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>나토 국방비 증액에도 생산 병목…기회 잡는 K-방산</t>
+          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>http://www.metroseoul.co.kr/article/20260707500477</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 16:54:00 +0900</t>
+          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E192">
-        <f>HYPERLINK("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg", IMAGE("//cdn.emetro.co.kr/data2/content/image/2026/07/07/.cache/512/20260707500478.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5048,44 +5047,20 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>곧 전장 뛰어들 피지컬 AI…“자율전투로 기술난제 극복”</t>
+          <t>[본지-대교협 공동기획中] 생성형 AI 기반 수업 혁신 확산 속 &amp;quot;인간 고유...</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004603882?sid=100</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=593399</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 17:46:00 +0900</t>
+          <t>Mon, 15 Jun 2026 09:00:00 +0900</t>
         </is>
       </c>
       <c r="E193">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/26/0004603882_001_20260326233246007.jpg?type=w800"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>193</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>[본지-대교협 공동기획中] 생성형 AI 기반 수업 혁신 확산 속 &amp;quot;인간 고유...</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=593399</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Mon, 15 Jun 2026 09:00:00 +0900</t>
-        </is>
-      </c>
-      <c r="E194">
         <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202606/593399_417079_4829_v150.jpg"))</f>
         <v/>
       </c>
@@ -5101,7 +5076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5137,21 +5112,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>** 황인홍 무주군수, 전북포럼서 방위산업 육성 전략 발제</t>
+          <t>** [기고] K방산, 무기 몇 대가 아니라 ‘전쟁 지속 능력’을 수출하라</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004171759?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003999494?sid=110</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 13:39:00 +0900</t>
+          <t>Sun, 20 Sep 2026 23:37:00 +0900</t>
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/09/20/0003999494_001_20260920234314419.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/09/20/0003999494_001_20260920234314419.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5161,21 +5136,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>** [뉴스1전북포럼] &amp;quot;전북 방산 육성, 인재·시험평가·실증 기반 갖춰야&amp;quot;(...</t>
+          <t>** 황인홍 무주군수, 전북포럼서 방위산업 육성 전략 발제</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009077130?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004171759?sid=102</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 13:00:00 +0900</t>
+          <t>Fri, 24 Jul 2026 13:39:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/24/0009077130_001_20260724130015189.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/24/0009077130_001_20260724130015189.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/07/24/0004171759_001_20260724133913936.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5185,21 +5160,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>** [뉴스1전북포럼]장원준 교수 &amp;quot;전북 방위산업 성공 조건은 첨단소재 플랫...</t>
+          <t>** [뉴스1전북포럼] &amp;quot;전북 방산 육성, 인재·시험평가·실증 기반 갖춰야&amp;quot;(...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009077035?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009077130?sid=102</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 12:08:00 +0900</t>
+          <t>Fri, 24 Jul 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E4">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/24/0009077035_001_20260724124415958.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/24/0009077035_001_20260724124415958.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/24/0009077130_001_20260724130015189.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/24/0009077130_001_20260724130015189.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5209,21 +5184,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>** [뉴스1 전북포럼] &amp;quot;전북 방산클러스터 선정은 시작에 불과, 전략 필요&amp;quot;</t>
+          <t>** [뉴스1전북포럼]장원준 교수 &amp;quot;전북 방위산업 성공 조건은 첨단소재 플랫...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009076971?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009077035?sid=102</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 11:51:00 +0900</t>
+          <t>Fri, 24 Jul 2026 12:08:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/24/0009076971_001_20260724115224904.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/24/0009076971_001_20260724115224904.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/24/0009077035_001_20260724124415958.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/24/0009077035_001_20260724124415958.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5233,21 +5208,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>** K방산 수출, 이제는 정보다 [기고]</t>
+          <t>** [뉴스1 전북포럼] &amp;quot;전북 방산클러스터 선정은 시작에 불과, 전략 필요&amp;quot;</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009076971?sid=102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
+          <t>Fri, 24 Jul 2026 11:51:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/24/0009076971_001_20260724115224904.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/24/0009076971_001_20260724115224904.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5257,21 +5232,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>** 포티투마루, ‘글로벌 디지털 포럼’에서 K-팔란티어 육성 전략 제시</t>
+          <t>** K방산 수출, 이제는 정보다 [기고]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2605499</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000927039?sid=110</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 21 Jul 2026 09:18:00 +0900</t>
+          <t>Thu, 23 Apr 2026 04:31:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/23/0000927039_001_20260423061157905.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5281,20 +5256,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>** 포티투마루, ‘글로벌 디지털 포럼’에서 K-팔란티어 육성 전략 제시</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.etoday.co.kr/news/view/2605499</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 09:18:00 +0900</t>
+        </is>
+      </c>
+      <c r="E8">
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721091456_2361804_1000_276.png"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>** [알립니다] 제2회 국방방산전략포럼 개최합니다</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://n.news.naver.com/mnews/article/011/0004602094?sid=100</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 20:46:00 +0900</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E9">
         <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/03/22/0004602094_001_20260323095513484.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/03/22/0004602094_001_20260323095513484.jpg?type=w800"))</f>
         <v/>
       </c>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260921024743", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260921024743"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260922045006", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260922045006"))</f>
         <v/>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260921024852", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260921024852"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260922045125", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260922045125"))</f>
         <v/>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260921024904", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260921024904"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260922045137", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260922045137"))</f>
         <v/>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260921024932", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260921024932"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260922045207", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260922045207"))</f>
         <v/>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260921025009", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260921025009"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260922045244", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260922045244"))</f>
         <v/>
       </c>
     </row>
@@ -3308,9 +3308,10 @@
           <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
         </is>
       </c>
-      <c r="E120">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
-        <v/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -3487,12 +3488,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3501,7 +3502,7 @@
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3511,12 +3512,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>전북대 방산AI부트캠프 소속 학생들 우수성 입증</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807915</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3525,7 +3526,7 @@
         </is>
       </c>
       <c r="E129">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807915_195513_1937_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4244,9 +4245,10 @@
           <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
-      <c r="E159">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
-        <v/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -5126,7 +5128,7 @@
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/09/20/0003999494_001_20260920234314419.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/09/20/0003999494_001_20260920234314419.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/09/20/0003999494_001_20260921102311866.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/09/20/0003999494_001_20260921102311866.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>전북대, 방산기업 15곳과 맞춤형 인재양성 프로그램 운영</t>
+          <t>美 지상·해양 방산사업 핵심축 '한화디펜스USA'…현지화 속도</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014200391?sid=102</t>
+          <t>https://news.mtn.co.kr/news-detail/2026092216533024563</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fri, 18 Sep 2026 16:41:00 +0900</t>
+          <t>Tue, 22 Sep 2026 17:50:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/09/22/2026092216533024563_00_228.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/09/22/2026092216533024563_00_228.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>첨단 드론 잇단 추락…방산 ‘무인 경쟁력’ 우려 확대</t>
+          <t>전북대, 방산기업 15곳과 맞춤형 인재양성 프로그램 운영</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1314054&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014200391?sid=102</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 15:00:00 +0900</t>
+          <t>Fri, 18 Sep 2026 16:41:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945", IMAGE("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -942,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>&amp;quot;민주당 맹목적 지지 벗어나 전북발전 성과 요구하자&amp;quot;…오창환 전북대 ...</t>
+          <t>첨단 드론 잇단 추락…방산 ‘무인 경쟁력’ 우려 확대</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002457143?sid=102</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1314054&amp;inflow=N</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 11:00:00 +0900</t>
+          <t>Thu, 17 Sep 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945", IMAGE("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945"))</f>
         <v/>
       </c>
     </row>
@@ -966,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>K방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
+          <t>&amp;quot;민주당 맹목적 지지 벗어나 전북발전 성과 요구하자&amp;quot;…오창환 전북대 ...</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002457143?sid=102</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 16:40:00 +0900</t>
+          <t>Thu, 17 Sep 2026 11:00:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -990,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
+          <t>K방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
+          <t>Tue, 15 Sep 2026 16:40:00 +0900</t>
         </is>
       </c>
       <c r="E24">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254595_266314_382_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1014,21 +1014,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
+          <t>사거리 100㎞, 분당 11발...차세대 K9 자주포의 조건은</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000953681?sid=100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
+          <t>Sun, 13 Sep 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E25">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/09/13/0000953681_001_20260913100015355.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1038,21 +1038,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
+          <t>김동관 한화 부회장, 크로아티아도 뚫었다…천무, 6400억 '수주'</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254410</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:58:00 +0900</t>
         </is>
       </c>
       <c r="E26">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202609/254410_266038_266_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1062,21 +1062,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
+          <t>[전북 24시] 전북대ㆍ공군미사일방어사령부, 방공·미사일방어 역량 강...</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000138022?sid=102</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
+          <t>Fri, 11 Sep 2026 16:35:00 +0900</t>
         </is>
       </c>
       <c r="E27">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/11/0000138022_001_20260911163511054.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1086,21 +1086,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
+          <t>전북대·미사일방어사령부, 미래 방공 역량 강화 '맞손'</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014184908?sid=102</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:59:00 +0900</t>
         </is>
       </c>
       <c r="E28">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/11/NISI20260911_0002236837_web_20260911145505_20260911150047363.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1110,21 +1110,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
+          <t>전북대 국방산업연구소-공군미사일방어사령부, 국방과학기술 연구·전문...</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003465967?sid=102</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
+          <t>Fri, 11 Sep 2026 14:13:00 +0900</t>
         </is>
       </c>
       <c r="E29">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/11/0003465967_001_20260911141311347.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1134,21 +1134,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
+          <t>13년 만에 다시 태국…한화오션, 함정 수출 사업 재개에 후속 사업 기대</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
+          <t>https://www.g-enews.com/view.php?ud=202609091411036783ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
+          <t>Wed, 09 Sep 2026 18:00:00 +0900</t>
         </is>
       </c>
       <c r="E30">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090914155308954ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1158,21 +1158,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
+          <t>[기획]수출 늘어난 K-방산, 협력사 지원도 늘렸다</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=887083</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1411337</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
+          <t>Tue, 08 Sep 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E31">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202609/1411337_1199637_2253_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1182,21 +1182,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
+          <t>양오봉 전북대 총장, ‘전고를 빛낸 사람들 상' 수상</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
+          <t>https://sjbnews.com/news/news.php?number=887083</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
+          <t>Tue, 08 Sep 2026 00:37:00 +0900</t>
         </is>
       </c>
       <c r="E32">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_887083_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1206,21 +1206,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
+          <t>전차 넘어 항공우주로…현대로템, 종합방산 도약 속도</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202609071405515543ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
+          <t>Mon, 07 Sep 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E33">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090716180300410ea14faf6f517512315593.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1230,21 +1230,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
+          <t>한화에어로, 무인차 아리온스멧 군 전력화 시동</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/417/0001157611?sid=101</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E34">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/417/2026/09/07/0001157611_001_20260907204017184.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1254,21 +1254,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
+          <t>[전북 24시] 전북대, 2027학년도 수시모집 총 3507명 선발</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137681?sid=102</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
+          <t>Mon, 07 Sep 2026 17:44:00 +0900</t>
         </is>
       </c>
       <c r="E35">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/07/0000137681_001_20260907174409598.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1278,21 +1278,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
+          <t>전북대 계약정원제 활용사업, 2차년도 산학 프로젝트 본격화</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597010</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
+          <t>Mon, 07 Sep 2026 11:28:00 +0900</t>
         </is>
       </c>
       <c r="E36">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597010_422691_2637_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1302,21 +1302,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
+          <t>KAI 경영참여 나선 한화…수출 시너지 기대 속 공급망 공정성 우려</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202609041512003756ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+          <t>Sun, 06 Sep 2026 18:26:00 +0900</t>
         </is>
       </c>
       <c r="E37">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026090416034800219ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1326,23 +1326,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
+          <t>‘과학수도’ 대전에 소부장 특화단지… K방산에 날개 단다</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002815979?sid=102</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Thu, 03 Sep 2026 09:19:00 +0900</t>
+        </is>
+      </c>
+      <c r="E38">
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/021/2026/09/03/0002815979_001_20260903100317784.jpg?type=w800"))</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1351,22 +1350,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
+          <t>한화그룹의 KAI 인수 추진 둘러싼 갑론을박, '규모의 경제' vs '경쟁 훼손...</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=446243</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E39">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
-        <v/>
+          <t>Wed, 02 Sep 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1375,21 +1375,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
+          <t>전북대, 거점국립대 패키지 지원 3개교 미선정</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=706959</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
+          <t>Tue, 01 Sep 2026 20:44:00 +0900</t>
         </is>
       </c>
       <c r="E40">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202609/706959_753996_4129_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
+          <t>지상·미사일·조선 전방위로…한화, 美 방산시장 공략 가속</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=202608281607092592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
+          <t>Sun, 30 Aug 2026 17:00:00 +0900</t>
         </is>
       </c>
       <c r="E41">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026082817014704212ea14faf6f5115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1423,21 +1423,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
+          <t>&amp;quot;그 어렵다는 미국 시장 문도 열었다&amp;quot; K9 자주포의 역사적 순간들</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000950861?sid=100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
+          <t>Sat, 29 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E42">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/29/0000950861_001_20260829100015512.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1447,21 +1447,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
+          <t>[대전 24시] 대전시, '방산 소부장 특화단지 지정' 총력</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000136760?sid=102</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
+          <t>Wed, 26 Aug 2026 10:10:00 +0900</t>
         </is>
       </c>
       <c r="E43">
-        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/26/0000136760_001_20260826101014760.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1471,21 +1471,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
+          <t>대전시-대전 국회의원, '방산소부장 특화단지 유치' 국회 토론회</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
+          <t>https://www.goodmorningcc.com/news/articleView.html?idxno=451224</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
+          <t>Tue, 25 Aug 2026 19:32:00 +0900</t>
         </is>
       </c>
       <c r="E44">
-        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg", IMAGE("https://cdn.goodmorningcc.com/news/thumbnail/202608/451224_466459_2226_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1495,21 +1495,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
+          <t>대전시, 방산 소부장 특화단지 지정 위한 국회 토론회 개최</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
+          <t>https://www.ccdn.co.kr/news/articleView.html?idxno=1095671</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
+          <t>Tue, 25 Aug 2026 18:23:00 +0900</t>
         </is>
       </c>
       <c r="E45">
-        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
+        <f>HYPERLINK("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg", IMAGE("https://cdn.ccdn.co.kr/news/thumbnail/202608/1095671_606589_1009_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1519,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
+          <t>대전시, '정부·기업·연구기관 국회에 모였다'... 방산 특화단지 필요...</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
+          <t>https://www.newsworker.co.kr/news/articleView.html?idxno=500829</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E46">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
+        <f>HYPERLINK("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg", IMAGE("https://cdn.newsworker.co.kr/news/photo/202608/500829_500910_198.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1543,21 +1543,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
+          <t>[K방산은 어떻게 세계를 뚫었나]①폴란드서 중동 거쳐 미국까지…4년 만...</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://hbnpress.com/news/view/1065597442480538</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1311286&amp;inflow=N</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
+          <t>Tue, 25 Aug 2026 17:20:00 +0900</t>
         </is>
       </c>
       <c r="E47">
-        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503", IMAGE("https://image.newstomato.com/newsimg/2026/8/25/1311286/attach.jpg?v=202608261503"))</f>
         <v/>
       </c>
     </row>
@@ -1567,21 +1567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
+          <t>대전, 방산 소부장 생태계 구축 나선다...국회 토론회서 경쟁력 점검</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
+          <t>https://hbnpress.com/news/view/1065597442480538</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E48">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
+        <f>HYPERLINK("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg", IMAGE("https://hbnpress.com/news/data/20260825/p1065597442480538_273_thum.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
+          <t>대전시, 방산 소부장 특화단지 유치전...'공감대 확산' 총력</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
+          <t>https://www.newstnt.com/news/articleView.html?idxno=715180</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:18:00 +0900</t>
         </is>
       </c>
       <c r="E49">
-        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202608/715180_717908_1554.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1615,21 +1615,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>전북대 이근회 석사과정생 차세대 RF 결합기 설계로 우수논문상.. '적은...</t>
+          <t>대전시, 방산 소부장 특화단지 지정 총력전…&amp;quot;국방 역량·과학기술 등 집...</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=628473</t>
+          <t>http://www.chungnamilbo.co.kr/news/articleView.html?idxno=905751</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 14:36:00 +0900</t>
+          <t>Tue, 25 Aug 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E50">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg", IMAGE("https://cdn.chungnamilbo.co.kr/news/thumbnail/202608/905751_483940_3556_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1639,21 +1639,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
+          <t>전북대 이근회 석사과정생 차세대 RF 결합기 설계로 우수논문상.. '적은...</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=628473</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
+          <t>Thu, 17 Sep 2026 14:36:00 +0900</t>
         </is>
       </c>
       <c r="E51">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/628473_542309_3415_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1663,21 +1663,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
+          <t>전북대 이상명 학생 연구장려금지원사업 선정.. '황계 화학작용제 검지...</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260908164442351</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=627410</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
+          <t>Fri, 11 Sep 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E52">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/627410_540905_2824_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1687,21 +1687,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
+          <t>신안보 혁신기업 육성 위한 '신속 조달체계 도입', 향후 보완 과제는</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
+          <t>https://www.ajunews.com/view/20260908164442351</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
+          <t>Tue, 08 Sep 2026 17:32:00 +0900</t>
         </is>
       </c>
       <c r="E53">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg", IMAGE("https://image.ajunews.com/content/image/2026/09/08/20260908164909547974.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1711,21 +1711,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
+          <t>전북대, 극한환경용 차세대 반도체 소자 개발</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
+          <t>https://www.naeil.com/news/read/601270?ref=naver</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
+          <t>Sun, 06 Sep 2026 22:02:00 +0900</t>
         </is>
       </c>
       <c r="E54">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1735,21 +1735,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
+          <t>[전북 24시] 전북대 배학열 교수팀, 극한환경서 활용할 차세대반도체 소...</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000137405?sid=102</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
+          <t>Thu, 03 Sep 2026 15:50:00 +0900</t>
         </is>
       </c>
       <c r="E55">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/09/03/0000137405_001_20260903155010615.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1759,21 +1759,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
+          <t>전북대 배학열 교수팀 초광대역갭 페로브스카이트 반도체 소자 개발.. '...</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=626020</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
+          <t>Thu, 03 Sep 2026 12:16:00 +0900</t>
         </is>
       </c>
       <c r="E56">
-        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202609/626020_539140_139_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1783,21 +1783,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
+          <t>대전, 국방 R&amp;amp;D 도시 넘어 방산 공급망 거점 노린다</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
+          <t>http://www.dailypop.kr/news/articleView.html?idxno=101907</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:40:00 +0900</t>
         </is>
       </c>
       <c r="E57">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg", IMAGE("http://www.dailypop.kr/news/thumbnail/202608/101907_169232_1125_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1807,21 +1807,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
+          <t>대전, 국회서 방산 소부장 특화단지 최적지 알려</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004654970?sid=102</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:33:00 +0900</t>
         </is>
       </c>
       <c r="E58">
-        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/011/2026/08/25/0004654970_001_20260825153318903.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1831,21 +1831,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
+          <t>“첨단 국방 중심지로”…대전시, 방산 소부장 특화단지 지정 논의 토론...</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
+          <t>https://www.sentv.co.kr/article/view/sentv202608250155</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:24:00 +0900</t>
         </is>
       </c>
       <c r="E59">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg", IMAGE("https://www.sentv.co.kr/data/sentv/image/2026/08/25/sentv20260825000143.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1855,21 +1855,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
+          <t>대전시, 'K-방산 심장' 정조준…국방 소부장 특화단지 유치 역량 모은다</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003460160?sid=102</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
+          <t>Tue, 25 Aug 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E60">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/25/0003460160_001_20260825193527510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1879,21 +1879,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
+          <t>한화 K9 자주포, 美 뚫었다… 獨·英 기업 제치고 ‘차륜형’ 수출</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003993895?sid=101</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:47:00 +0900</t>
         </is>
       </c>
       <c r="E61">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/08/20/0003993895_001_20260820095824854.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1903,21 +1903,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
+          <t>한화, 美 육군 뚫었다…K9 자주포 계약금만 '무려'</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
+          <t>https://n.news.naver.com/mnews/article/374/0000528273?sid=101</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 18:28:00 +0900</t>
         </is>
       </c>
       <c r="E62">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/374/2026/08/19/0000528273_001_20260820074610873.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1927,21 +1927,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
+          <t>美 '함정 건조' 문 열리나···K조선에 남을 진짜 실익은?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260817500461</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460421</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:00:00 +0900</t>
         </is>
       </c>
       <c r="E63">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260922045006", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260922045006"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460421_1301267_1921_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -1951,21 +1951,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
+          <t>‘20조’ 美 함정 MRO 시장⋯ K-조선, 7함대 중심 낙수효과 커진다</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
+          <t>https://www.viva100.com/article/20260817500461</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
+          <t>Mon, 17 Aug 2026 15:32:00 +0900</t>
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260923032514", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260923032514"))</f>
         <v/>
       </c>
     </row>
@@ -1975,21 +1975,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
+          <t>피라미드 상공까지 열어준 이집트... K9으로 쌓인 신뢰의 무게</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000948256?sid=100</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
+          <t>Sun, 16 Aug 2026 10:00:00 +0900</t>
         </is>
       </c>
       <c r="E65">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/08/16/0000948256_001_20260816100017616.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +1999,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
+          <t>한국서 美 군함 만들 길 열렸다…트럼프, 최대 2척 해외 건조 허용</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000633625?sid=101</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
+          <t>Fri, 14 Aug 2026 21:40:00 +0900</t>
         </is>
       </c>
       <c r="E66">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/08/14/2026081490276_thumb_214629_20260814215027794.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2023,21 +2023,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
+          <t>한화, KAI 이어 오스탈까지…확대되는 ‘한국판 록히드마틴’ 구상</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260806162915186</t>
+          <t>https://www.g-enews.com/view.php?ud=202608121305118853ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
+          <t>Wed, 12 Aug 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E67">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026081213290302924ea14faf6f521123420134.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2047,21 +2047,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
+          <t>美 무기 구매서 첨단기술 협력 국가로… K-방산 '눈부신 발전'</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
+          <t>https://www.ajunews.com/view/20260806162915186</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
+          <t>Thu, 06 Aug 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E68">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg", IMAGE("https://image.ajunews.com/content/image/2026/08/06/20260806203329192695.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2071,21 +2071,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
+          <t>글로벌 방산 트렌드는 ‘합종연횡’…한화, KAI와 손잡나</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
+          <t>https://n.news.naver.com/mnews/article/262/0000019567?sid=101</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
+          <t>Sun, 02 Aug 2026 17:01:00 +0900</t>
         </is>
       </c>
       <c r="E69">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/262/2026/08/02/0000019567_001_20260802193510142.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2095,21 +2095,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
+          <t>김종출 KAI 대표, 완제기 제조 역량에 'AI·위성 기술' 입힌다</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=251282</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:12:00 +0900</t>
         </is>
       </c>
       <c r="E70">
-        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/251282_261914_1843_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2119,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
+          <t>모레, 전북대와 피지컬 AI 기술 이전 계약 ··· 공간지능형 AI 플랫폼 ...</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
+          <t>https://www.datanet.co.kr/news/articleView.html?idxno=213400</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
+          <t>Wed, 29 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E71">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
+        <f>HYPERLINK("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg", IMAGE("https://cdn.datanet.co.kr/news/thumbnail/202607/213400_137602_1023_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2143,21 +2143,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
+          <t>[트럼프發 훈풍 K-조선] '기회의 문' 열린 美함정시장… 현지투자·경쟁...</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260730010011003</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E72">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/30d/2026073001001986500110031.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2167,21 +2167,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
+          <t>[전북24시]전북대 피지컬 AI 원천기술 이전 상용화된다</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134807?sid=102</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:20:00 +0900</t>
         </is>
       </c>
       <c r="E73">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/29/0000134807_001_20260729182012243.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2191,21 +2191,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
+          <t>전북대 산학협력단-(주)모레, AI 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1047952</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 18:18:00 +0900</t>
         </is>
       </c>
       <c r="E74">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -2215,21 +2215,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
+          <t>전북대 피지컬 AI 원천기술, 기업 통해 상용화 길 열었다</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607290020</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806724</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:52:00 +0900</t>
         </is>
       </c>
       <c r="E75">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806724_194383_5015_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2239,21 +2239,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
+          <t>전북대, 피지컬 AI 기술 3건 모레에 이전…3억5000만원 규모</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
+          <t>https://www.betanews.net/article/view/beta202607290020</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
+          <t>Wed, 29 Jul 2026 14:20:00 +0900</t>
         </is>
       </c>
       <c r="E76">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/29/beta20260729000023.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2263,21 +2263,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
+          <t>K-방산, AI 파트너 확보전…기술 협력망이 새 경쟁력</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
+          <t>https://www.g-enews.com/view.php?ud=202607290914253246ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
+          <t>Wed, 29 Jul 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E77">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026072909481700554ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2287,21 +2287,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
+          <t>AI가 드론·무인이동체 지휘…모레, 전북대 피지컬AI 기술 확보</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005392655?sid=101</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:00:00 +0900</t>
         </is>
       </c>
       <c r="E78">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/008/2026/07/29/0005392655_001_20260729120120057.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2311,21 +2311,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
+          <t>전북대-모레, 전역 위치결정 등 피지컬AI 3건 기술이전 계약 체결</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003452135?sid=102</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
+          <t>Wed, 29 Jul 2026 11:29:00 +0900</t>
         </is>
       </c>
       <c r="E79">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/07/29/0003452135_001_20260729112916151.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2335,21 +2335,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
+          <t>[무기 된 AI, K방산 좌표]①방산 4社 AI 무장 끝냈지만…낡은 인증제도가...</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005796140?sid=101</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
+          <t>Wed, 29 Jul 2026 10:47:00 +0900</t>
         </is>
       </c>
       <c r="E80">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/29/0005796140_001_20260729154910966.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2359,21 +2359,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
+          <t>[2027수시특집] 전북대 3152명(76.7%) '확대'.. 교과 지역의사선발 21명 '...</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623328</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
+          <t>Fri, 28 Aug 2026 16:52:00 +0900</t>
         </is>
       </c>
       <c r="E81">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623328_536420_1346_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2383,21 +2383,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
+          <t>[K방산 리더 한화] 현지화에 달린 해외수주… 한화오션 '패키지형 수출...</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260825010008064</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
+          <t>Mon, 24 Aug 2026 18:04:00 +0900</t>
         </is>
       </c>
       <c r="E82">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png", IMAGE("https://img.asiatoday.co.kr/file/2026y/08m/25d/20260825010008064_1787563928_1.png"))</f>
         <v/>
       </c>
     </row>
@@ -2407,21 +2407,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
+          <t>방산 완전체 만드는 현대차그룹…현대로템 영토 확장 승부수</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1404584</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E83">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1404584_1192641_483_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2431,21 +2431,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
+          <t>1.9조 전자전기 사업 ‘흔들’…방산 비리 의혹에 지연 우려</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1310971&amp;inflow=N</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
+          <t>Fri, 21 Aug 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E84">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810", IMAGE("https://image.newstomato.com/newsimg/2026/8/21/1310971/attach.jpg?v=202608240810"))</f>
         <v/>
       </c>
     </row>
@@ -2455,21 +2455,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>'방산기업 미래 전략은?' 3회 전북 방위산업 육성 세미나</t>
+          <t>전북대학교, 탈레스코리아 'STEM for ALL' 국내 첫 장학생 배출</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014139089?sid=102</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208980</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:02:00 +0900</t>
+          <t>Fri, 21 Aug 2026 08:20:00 +0900</t>
         </is>
       </c>
       <c r="E85">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208980_478004_3519_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2479,21 +2479,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
+          <t>'방산기업 미래 전략은?' 3회 전북 방위산업 육성 세미나</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260819500013</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014139089?sid=102</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
+          <t>Thu, 20 Aug 2026 17:02:00 +0900</t>
         </is>
       </c>
       <c r="E86">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260922045125", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260922045125"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/20/NISI20260820_0002217273_web_20260820164120_20260820170319831.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2503,21 +2503,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
+          <t>협약서가 ‘인재’로 돌아왔다…전북대 방산인재 육성 첫 결실</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
+          <t>https://www.viva100.com/article/20260819500013</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
+          <t>Wed, 19 Aug 2026 08:38:00 +0900</t>
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260923032627", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260923032627"))</f>
         <v/>
       </c>
     </row>
@@ -2527,21 +2527,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
+          <t>전북대·탈레스, 방산 인재양성 협력 확대···첫 장학생 배출</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2460271</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
+          <t>Tue, 18 Aug 2026 16:00:00 +0900</t>
         </is>
       </c>
       <c r="E88">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202608/2460271_1301087_1819_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2551,21 +2551,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
+          <t>서울대 10개 만들기 선정 임박…'피지컬AI' 전북대 포함될까</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009116420?sid=102</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
+          <t>Sun, 16 Aug 2026 16:38:00 +0900</t>
         </is>
       </c>
       <c r="E89">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/16/0009116420_001_20260817105908783.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2575,21 +2575,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
+          <t>전북대학교, AI와 지역 전략산업 결합한 석·박사급 인재 150명 키운다</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260812500685</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208482</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
+          <t>Fri, 14 Aug 2026 09:46:00 +0900</t>
         </is>
       </c>
       <c r="E90">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260922045137", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260922045137"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208482_477346_3211_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2599,21 +2599,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
+          <t>필리 이어 오스탈까지… 한화, 美 해군•핵잠 노린다</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
+          <t>https://www.viva100.com/article/20260812500685</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
+          <t>Wed, 12 Aug 2026 15:00:00 +0900</t>
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260923032642", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260923032642"))</f>
         <v/>
       </c>
     </row>
@@ -2623,21 +2623,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
+          <t>전북대 '휘둥그레' 팀, 대학생 AI 자율주행 경진대회 대상</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009108391?sid=102</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:29:00 +0900</t>
         </is>
       </c>
       <c r="E92">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/08/11/0009108391_001_20260811163012621.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2647,21 +2647,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
+          <t>전북대, 자율주행 전국대회서 '대상'…AI·미래차 기술력 입증</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
+          <t>https://n.news.naver.com/mnews/article/629/0000523577?sid=102</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
+          <t>Tue, 11 Aug 2026 16:22:00 +0900</t>
         </is>
       </c>
       <c r="E93">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/629/2026/08/11/202624401786429971_20260811162210657.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2671,21 +2671,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
+          <t>한화, KAI ‘인수’ 성큼…완주까지 넘어야 할 산</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309851&amp;inflow=N</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
+          <t>Tue, 11 Aug 2026 10:38:00 +0900</t>
         </is>
       </c>
       <c r="E94">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426", IMAGE("https://image.newstomato.com/newsimg/2026/8/11/1309851/attach.jpg?v=202608111426"))</f>
         <v/>
       </c>
     </row>
@@ -2695,21 +2695,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
+          <t>전북대, 석·박사급 인공지능 전문인력 150명 양성</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=855479</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
+          <t>Sun, 09 Aug 2026 16:48:00 +0900</t>
         </is>
       </c>
       <c r="E95">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202608/855479_875351_4720_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2719,21 +2719,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
+          <t>전북대, 지역 성장엔진 'AI+X 석·박사' 인재 양성 나선다</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=807560</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
+          <t>Sat, 08 Aug 2026 15:58:00 +0900</t>
         </is>
       </c>
       <c r="E96">
-        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202608/807560_195196_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2743,21 +2743,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
+          <t>전북대, 7개 융합학과로 AI+X 고급인재 150명 양성한다</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
+          <t>https://www.kyosu.net/news/articleView.html?idxno=208585</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
+          <t>Fri, 07 Aug 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E97">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg", IMAGE("https://cdn.kyosu.net/news/photo/202608/208585_209853_4310.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2767,21 +2767,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
+          <t>전북대 AI+X 고급인재 양성 나선다.. 학사~박사 최단 5.5년 '패스트트랙...</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622397</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:54:00 +0900</t>
         </is>
       </c>
       <c r="E98">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622397_535480_5228_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2791,21 +2791,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
+          <t>전북대, AX 학사~박사까지 8년→최단 5.5년 가능…톱 100 AI 특화대학원...</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003455196?sid=102</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
+          <t>Fri, 07 Aug 2026 11:43:00 +0900</t>
         </is>
       </c>
       <c r="E99">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/07/0003455196_001_20260813164059037.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2815,21 +2815,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
+          <t>[한화 책임경영 2막] 육·해·공·우주 연결…김동관, 방산 도약 이끈다</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202608051534469874112616b072_1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
+          <t>Wed, 05 Aug 2026 16:44:00 +0900</t>
         </is>
       </c>
       <c r="E100">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080516075702899112616b072210113354.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2839,21 +2839,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
+          <t>하드킬 빠진 대드론 국가표준…조달 지연·재설계 우려</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
+          <t>https://www.g-enews.com/view.php?ud=202608041148056786ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
+          <t>Tue, 04 Aug 2026 16:02:00 +0900</t>
         </is>
       </c>
       <c r="E101">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026080411530101753ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -2863,21 +2863,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
+          <t>실적은 ‘훨훨’ 수출은 ‘주춤’…K방산 ‘성장 지속성’ 기로</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260726500503</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1309035&amp;inflow=N</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
+          <t>Mon, 03 Aug 2026 15:20:00 +0900</t>
         </is>
       </c>
       <c r="E102">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260922045207", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260922045207"))</f>
+        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239", IMAGE("https://image.newstomato.com/newsimg/2026/8/3/1309035/attach.jpg?v=202608041239"))</f>
         <v/>
       </c>
     </row>
@@ -2887,21 +2887,21 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
+          <t>‘MASGA’ 출범했지만⋯ K-조선 수혜규모, 워싱턴서 갈린다</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
+          <t>https://www.viva100.com/article/20260726500503</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
+          <t>Sun, 26 Jul 2026 15:42:00 +0900</t>
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260923032712", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260923032712"))</f>
         <v/>
       </c>
     </row>
@@ -2911,12 +2911,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
+          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2935,21 +2935,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
+          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
+          <t>Fri, 24 Jul 2026 04:33:00 +0900</t>
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2959,21 +2959,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
+          <t>전북대 “K-방산 인재·산업 거점으로 도약”</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735992?sid=102</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
+          <t>Thu, 23 Jul 2026 14:48:00 +0900</t>
         </is>
       </c>
       <c r="E106">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/23/0003735992_001_20260723144820137.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2983,21 +2983,21 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
+          <t>[차세현의 직격토론] “미국 군함 건조하면 나토 시장 K방산에 활짝 열...</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003539208?sid=110</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
+          <t>Wed, 22 Jul 2026 00:14:00 +0900</t>
         </is>
       </c>
       <c r="E107">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/22/0003539208_001_20260722053717880.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3007,21 +3007,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
+          <t>김동관 한화 부회장, '전 공정 현지 생산'으로 미국 방산 '벽' 깬다</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250489</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
+          <t>Mon, 20 Jul 2026 16:36:00 +0900</t>
         </is>
       </c>
       <c r="E108">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250489_260882_4746_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3031,21 +3031,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
+          <t>&amp;quot;방위산업 육성 어떻게&amp;quot;…뉴스1 전북, '방위산업의 육성 방향과 전략'</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009068290?sid=102</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
+          <t>Mon, 20 Jul 2026 13:20:00 +0900</t>
         </is>
       </c>
       <c r="E109">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/07/20/0009068290_001_20260720132107280.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3055,21 +3055,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
+          <t>'유럽 방산블록'에 수주 주춤…K방산 승부처는</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071616414621415</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
+          <t>Thu, 16 Jul 2026 17:54:00 +0900</t>
         </is>
       </c>
       <c r="E110">
-        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/nI2ssJxqQACaSEQc/image/20260716_173100//2026071617302XeaDzYQ_06.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3079,21 +3079,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
+          <t>유럽 '방산 블록' 본격화, K-방산 새 수출 전략이 필요하다</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
+          <t>https://bizhankook.com/articles/k-defense-europe-future-strategy.html</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
+          <t>Thu, 16 Jul 2026 15:48:00 +0900</t>
         </is>
       </c>
       <c r="E111">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
+        <f>HYPERLINK("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg", IMAGE("https://s.bizhankook.com/attachments_og/2026/07/134680_og_4b86a4ce.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3103,21 +3103,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
+          <t>4조짜리 태국 호위함 잡아라…조선 '빅2' 수주전 곧 결판난다</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250247</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
+          <t>Wed, 15 Jul 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E112">
-        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250247_260717_3649_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3127,21 +3127,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
+          <t>'4兆' 태국 호위함 수주 눈앞…한화오션, 해외 함정시장 판 키운다</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260714135200349</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260715010005591</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
+          <t>Wed, 15 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E113">
-        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/16d/2026071501001031000055911.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3151,21 +3151,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
+          <t>[불붙는 KAI 인수전] 한화·현대차·LIG 이유 있는 3社 3色 러브콜</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
+          <t>https://www.ajunews.com/view/20260714135200349</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
+          <t>Wed, 15 Jul 2026 05:02:00 +0900</t>
         </is>
       </c>
       <c r="E114">
-        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
+        <f>HYPERLINK("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png", IMAGE("https://image.ajunews.com/content/image/2026/07/14/20260714140853822373.png"))</f>
         <v/>
       </c>
     </row>
@@ -3175,21 +3175,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
+          <t>[시사천국] 드론이 바꾼 전쟁의 문법…평화를 위한 K-방산의 과제는?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
+          <t>https://news.cpbc.co.kr/article/1174362?division=NAVER</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
+          <t>Tue, 14 Jul 2026 22:54:00 +0900</t>
         </is>
       </c>
       <c r="E115">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg", IMAGE("https://img.cpbc.co.kr/newsimg/upload/2026/07/14/6oH1784030232565.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3199,21 +3199,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
+          <t>MASGA 길 따라 ‘1600조’ 美 군함 시장 열릴까</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001860745?sid=101</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
+          <t>Tue, 14 Jul 2026 00:09:00 +0900</t>
         </is>
       </c>
       <c r="E116">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/14/2026071319551076971_1783940110_1783854842_20260714000906755.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3223,21 +3223,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
+          <t>[K함정 수출, 다음 전선] 성능만으론 부족…K함정 후속 수주전의 세 가...</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
+          <t>https://www.g-enews.com/view.php?ud=202607131543012473ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
+          <t>Mon, 13 Jul 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E117">
-        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026071316024508909ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3247,21 +3247,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
+          <t>'동맹 우선' 나토 블록화에 K방산, 유럽 시장 진출 '비상등' 켜지나</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
+          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=250034</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
+          <t>Mon, 13 Jul 2026 14:18:00 +0900</t>
         </is>
       </c>
       <c r="E118">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg", IMAGE("https://cdn.insightkorea.co.kr/news/thumbnail/202607/250034_260376_2728_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3271,21 +3271,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
+          <t>[포커스] 캐나다선 고배 마셨지만…&amp;quot;글로벌 군함 수주전, 지금부터 시작...</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.viva100.com/article/20260712500414</t>
+          <t>https://n.news.naver.com/mnews/article/448/0000626219?sid=101</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
+          <t>Sun, 12 Jul 2026 19:33:00 +0900</t>
         </is>
       </c>
       <c r="E119">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260922045244", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260922045244"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/12/2026071290147_thumb_074550_20260712195025659.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3295,23 +3295,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
+          <t>K-조선 미련⋯ 캐나다, 북극항로·해양안보 매력 못 잊어</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
+          <t>https://www.viva100.com/article/20260712500414</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 12 Jul 2026 14:06:00 +0900</t>
+        </is>
+      </c>
+      <c r="E120">
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260923032750", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260923032750"))</f>
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -3320,22 +3319,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
+          <t>한화, KAI에 '2.5兆' 베팅… '육해공 통합 방산' 퍼즐 맞춘다</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
+          <t>https://www.asiatoday.co.kr/kn/view.php?key=20260710010003712</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
-        </is>
-      </c>
-      <c r="E121">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
-        <v/>
+          <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -3344,21 +3344,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
+          <t>유럽 방산시장 '새 판'···나토가 선택할 K방산 기업의 조건은?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.news2day.co.kr/article/20260709500128</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2447247</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
+          <t>Thu, 09 Jul 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E122">
-        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202607/2447247_1285242_2338_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3368,21 +3368,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
+          <t>[방산 이슈 진단 (152)] 캐나다 잠수함 사업, ‘20조원+α’인 사업 규모...</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
+          <t>https://www.news2day.co.kr/article/20260709500128</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
+          <t>Thu, 09 Jul 2026 11:32:00 +0900</t>
         </is>
       </c>
       <c r="E123">
-        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png", IMAGE("https://cdn.news2day.co.kr/data2/content/image/2026/07/09/.cache/512/20260709500125.png"))</f>
         <v/>
       </c>
     </row>
@@ -3392,21 +3392,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
+          <t>[시선집중] 방산전문가 &amp;quot;李대통령, 나토 방산시장 '혈 뚫었다'...공동개...</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
+          <t>https://n.news.naver.com/mnews/article/214/0001510555?sid=100</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
+          <t>Thu, 09 Jul 2026 10:17:00 +0900</t>
         </is>
       </c>
       <c r="E124">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
+        <f>HYPERLINK("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg", IMAGE("https://ssl.pstatic.net/static.news/image/news/ogtag/navernews_800x420_20221201.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3416,21 +3416,21 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
+          <t>[나토 문턱에 선 K-잠수함] 전문가들 “최종 경합 자체가 레퍼런스”…...</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
+          <t>https://www.g-enews.com/view.php?ud=202607081433085592ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:16:00 +0900</t>
         </is>
       </c>
       <c r="E125">
-        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026070815032001444ea14faf6f51831011667.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3440,21 +3440,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
+          <t>[나토 문턱에 선 K-잠수함] 캐나다가 택한 건 잠수함 너머 ‘안보 생태...</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
+          <t>https://www.g-enews.com/view.php?ud=20260708150048725924debea800_1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
+          <t>Wed, 08 Jul 2026 19:14:00 +0900</t>
         </is>
       </c>
       <c r="E126">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=202607081501470451524debea800115951676.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3464,21 +3464,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
+          <t>“나토 높은 벽” 뚫는 李 승부수, 조달협정…“우회로 뚫는 효과”</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003536241?sid=100</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
+          <t>Wed, 08 Jul 2026 17:27:00 +0900</t>
         </is>
       </c>
       <c r="E127">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/07/08/0003536241_001_20260709124354571.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3488,21 +3488,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
+          <t>전북대학교 방산AI부트캠프, 전국 자율주행 경진대회서 대상·동상 동시...</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=208485</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
+          <t>Sun, 16 Aug 2026 07:16:00 +0900</t>
         </is>
       </c>
       <c r="E128">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202608/208485_477349_3721_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3536,21 +3536,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
+          <t>[전북24시] 전북대 반도체공동연구소, 반도체 인재양성 전공경계 허문다</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000135737?sid=102</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
+          <t>Tue, 11 Aug 2026 17:18:00 +0900</t>
         </is>
       </c>
       <c r="E130">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/08/11/0000135737_001_20260811171820346.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3560,21 +3560,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
+          <t>전북대 방산AI부트캠프사업단 자율주행 경진대회 대상/동상 석권.. AI자...</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=622755</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
+          <t>Tue, 11 Aug 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E131">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/622755_535846_2732_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3584,21 +3584,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
+          <t>전북대, 전국 대학생 AI 자율주행 경진대회서 대상·동상</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014119994?sid=102</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
+          <t>Tue, 11 Aug 2026 11:34:00 +0900</t>
         </is>
       </c>
       <c r="E132">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/11/NISI20260811_0002209461_web_20260811113250_20260811113514916.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3608,21 +3608,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
+          <t>에스토니아서 '천둥'이라 부르는 K9 자주포... 전 방위사업청장이 말하...</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000944797?sid=100</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
+          <t>Tue, 28 Jul 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E133">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/28/0000944797_001_20260728140118726.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3632,21 +3632,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
+          <t>200억 더 깎자는 말에 문재인의 대답... K9 계약 살렸다</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942173?sid=100</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
+          <t>Tue, 14 Jul 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E134">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/14/0000942173_001_20260728105813570.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3656,21 +3656,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
+          <t>서명식 당일 무산된 K9 자주포 계약…이집트는 &amp;quot;가격 더 깎아달라&amp;quot; 요구...</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000939478?sid=100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
+          <t>Tue, 30 Jun 2026 14:14:00 +0900</t>
         </is>
       </c>
       <c r="E135">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/30/0000939478_001_20260630141412552.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3680,21 +3680,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
+          <t>&amp;quot;한국 배우고 싶다&amp;quot; 눈물 글썽인 대통령… K9 자주포로 동반자된 이집트</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000936758?sid=100</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
+          <t>Tue, 16 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E136">
-        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/16/0000936758_001_20260616140113437.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3704,21 +3704,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
+          <t>전북은행, 직원과의 직접 소통으로 경영전략 반영…하림, 지역 초등 장...</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
+          <t>https://www.sisaon.co.kr/news/articleView.html?idxno=201832</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
+          <t>Mon, 15 Jun 2026 11:06:00 +0900</t>
         </is>
       </c>
       <c r="E137">
-        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
+        <f>HYPERLINK("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg", IMAGE("https://cdn.sisaon.co.kr/news/photo/202606/201832_302679_5520.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3728,21 +3728,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
+          <t>지자체-정치권-학계 '찰떡공조' 빛나</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://www.jjan.kr/article/20260614500064</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1043516</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
+          <t>Sun, 14 Jun 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E138">
-        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
+        <f>HYPERLINK("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png", IMAGE("http://www.jjn.co.kr/image/logo/snslogo_20220512034033.png"))</f>
         <v/>
       </c>
     </row>
@@ -3752,21 +3752,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
+          <t>방산혁신클러스터 선정 의미와 남은 과제</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
+          <t>https://www.jjan.kr/article/20260614500064</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
+          <t>Sun, 14 Jun 2026 15:06:00 +0900</t>
         </is>
       </c>
       <c r="E139">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg", IMAGE("https://cdn.jjan.kr/data2/content/image/2026/06/14/.cache/512/20260614500348.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3776,21 +3776,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
+          <t>전북·전주 방산클러스터 선정…지자체·정치권·학계 '삼각 공조' 결실</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009001684?sid=102</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
+          <t>Sat, 13 Jun 2026 10:37:00 +0900</t>
         </is>
       </c>
       <c r="E140">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/06/13/0009001684_001_20260613103710152.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3800,21 +3800,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
+          <t>유통기한 지난 라면 먹으며 버텼다...K9 이집트 '2조' 수출의 주역은</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000934040?sid=100</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 14:01:00 +0900</t>
+          <t>Tue, 02 Jun 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E141">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/06/02/0000934040_001_20260602144013083.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3824,21 +3824,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
+          <t>미국 장비 분해로 시작...'독자 개발' K9, 세계 자주포 시장 절반 삼켰다</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000931558?sid=100</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 22:30:00 +0900</t>
+          <t>Tue, 19 May 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E142">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/19/0000931558_001_20260519140123824.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3848,21 +3848,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
+          <t>전북대, 방사청 '국방사업관리사' 교육 2년 연속 주관기관 선정</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=439938</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 14:38:00 +0900</t>
+          <t>Sun, 17 May 2026 22:30:00 +0900</t>
         </is>
       </c>
       <c r="E143">
-        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202605/439938_149008_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3872,21 +3872,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
+          <t>'방산 전문인력' 전북서 키운다···전북대, 교육과정 재학생·현장 투...</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
+          <t>http://www.enewstoday.co.kr/news/articleView.html?idxno=2429866</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 13:07:00 +0900</t>
+          <t>Fri, 15 May 2026 14:38:00 +0900</t>
         </is>
       </c>
       <c r="E144">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg", IMAGE("https://cdn.enewstoday.co.kr/news/thumbnail/202605/2429866_1264342_3744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3896,21 +3896,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
+          <t>“방산 인재 키운다”…전북대, 국방사업관리사 교육 2년 연속 맡는다</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002441535?sid=102</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Fri, 15 May 2026 11:26:00 +0900</t>
+          <t>Fri, 15 May 2026 13:07:00 +0900</t>
         </is>
       </c>
       <c r="E145">
-        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/05/15/0002441535_001_20260515130711426.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3920,21 +3920,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
+          <t>전북대, K-방산 도약 이끌 국방사업관리 전문 인력 양성 박차</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=592587</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 14:00:00 +0900</t>
+          <t>Fri, 15 May 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E146">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202605/592587_415811_246_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -3944,21 +3944,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
+          <t>尹정부 예산 삭감에 날개 꺾였던 K방산... 향후 3년이 골든타임이다</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000929083?sid=100</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Mon, 04 May 2026 17:30:00 +0900</t>
+          <t>Tue, 05 May 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E147">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/05/0000929083_001_20260505140023438.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3968,21 +3968,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>추미애, 핵심 공약 직접 챙긴다</t>
+          <t>[뉴스이용자위원회] &amp;quot;유익하지만 유료화 가능할까 의문... 심층 기획이 ...</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000928975?sid=103</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 17:08:00 +0900</t>
+          <t>Mon, 04 May 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E148">
-        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/05/04/0000928975_001_20260505061121922.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3992,21 +3992,21 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
+          <t>추미애, 핵심 공약 직접 챙긴다</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
+          <t>http://www.suwonilbo.kr/news/articleView.html?idxno=315789</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
+          <t>Fri, 01 May 2026 17:08:00 +0900</t>
         </is>
       </c>
       <c r="E149">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg", IMAGE("https://cdn.suwonilbo.kr/news/photo/202605/315789_220410_00.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4016,21 +4016,21 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
+          <t>전북대, 피지컬AI 국방·항공우주·로봇·자율제조 분야 최신 기술 공유</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202604240028</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003421490?sid=102</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
+          <t>Fri, 24 Apr 2026 17:19:00 +0900</t>
         </is>
       </c>
       <c r="E150">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/24/0003421490_001_20260424171913080.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4040,21 +4040,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
+          <t>전북대 주도 AI 학술대회 무주서 열렸다…국방·로봇 핵심 기술 총집결</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
+          <t>https://www.betanews.net/article/view/beta202604240028</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
+          <t>Fri, 24 Apr 2026 14:16:00 +0900</t>
         </is>
       </c>
       <c r="E151">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/04/24/beta20260424000033.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4064,21 +4064,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
+          <t>피지컬AI 중심 첨단 연구 성과 전북대에서 공유</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=607296</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
+          <t>Fri, 24 Apr 2026 13:52:00 +0900</t>
         </is>
       </c>
       <c r="E152">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202604/607296_520659_5152_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4088,21 +4088,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
+          <t>방사청, '거짓말' 의혹에 청와대 감사까지 받았지만…KF-21 탄생의 씨앗...</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000926654?sid=100</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
+          <t>Tue, 21 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E153">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/21/0000926654_001_20260421140118894.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4112,21 +4112,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
+          <t>&amp;quot;전북, 더 이상 방산 변방 아냐... 소재·부품·드론 잇는 전략 심장으로...</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=798091</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
+          <t>Mon, 20 Apr 2026 17:10:00 +0900</t>
         </is>
       </c>
       <c r="E154">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/798091_185937_96_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4136,21 +4136,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
+          <t>“5~6년 내 전북이 K-방산 핵심축 될 것”…군산김제부안을 '출사표' 던...</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002438263?sid=102</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
+          <t>Mon, 20 Apr 2026 16:57:00 +0900</t>
         </is>
       </c>
       <c r="E155">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/20/0002438263_001_20260420175215332.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4160,21 +4160,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
+          <t>김병주 &amp;quot;전북 탄소가 K-방산 뼈대 만들 것&amp;quot;</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=797974</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
+          <t>Sun, 19 Apr 2026 14:00:00 +0900</t>
         </is>
       </c>
       <c r="E156">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202604/797974_185814_5559_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4184,21 +4184,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
+          <t>[단독]‘친명’ 청와대 인사 추가 출사표…이광수 전 선임행정관 “전북...</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000342149?sid=100</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
+          <t>Fri, 17 Apr 2026 20:18:00 +0900</t>
         </is>
       </c>
       <c r="E157">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/04/17/0000342149_001_20260417201911556.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4208,21 +4208,21 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
+          <t>국회, K-방산 공급망 세미나 열려…'민관 협력·인증 생태계' 구축 시급</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003417631?sid=105</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+          <t>Tue, 14 Apr 2026 13:42:00 +0900</t>
         </is>
       </c>
       <c r="E158">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/04/14/0003417631_001_20260414194718930.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4232,23 +4232,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
+          <t>'K-방산' 미래 경쟁력 강화, 전북 기업과 머리 맞대</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037820</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+          <t>Sun, 12 Apr 2026 18:28:00 +0900</t>
+        </is>
+      </c>
+      <c r="E159">
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037820_263332_274_v150.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="160">
@@ -4257,21 +4256,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
+          <t>K방산 경쟁력 확보 정책적 지원 방향 모색</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
+          <t>https://kookbang.dema.mil.kr/newsWeb/20260413/2/ATCE_CTGR_0010020000/view.do</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
+          <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E160">
-        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
+        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4281,21 +4280,21 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
+          <t>이용철 방위사업청장, 전북서 'K-방산 미래 경쟁력' 해법 찾는다</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
+          <t>http://www.jeonmin.co.kr/news/articleView.html?idxno=437704</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
+          <t>Sun, 12 Apr 2026 12:34:00 +0900</t>
         </is>
       </c>
       <c r="E161">
-        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
+        <f>HYPERLINK("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg", IMAGE("http://www.jeonmin.co.kr/news/thumbnail/202604/437704_146952_2517_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4305,21 +4304,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
+          <t>전북대 찾은 방사청…K방산 공급망 재편 신호</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
+          <t>https://www.newsfreezone.co.kr/news/articleView.html?idxno=684675</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
+          <t>Fri, 10 Apr 2026 19:56:00 +0900</t>
         </is>
       </c>
       <c r="E162">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg", IMAGE("https://cdn.newsfreezone.co.kr/news/thumbnail/202604/684675_727738_5335_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4329,21 +4328,21 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
+          <t>방사청-전북 방산기업 간담회…공급망 자립·지역산업 활성화 모색</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
+          <t>https://n.news.naver.com/mnews/article/421/0008883068?sid=100</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
+          <t>Fri, 10 Apr 2026 17:30:00 +0900</t>
         </is>
       </c>
       <c r="E163">
-        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/421/2026/04/10/0008883068_001_20260410212912290.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4353,21 +4352,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
+          <t>이돈승 완주군수 예비후보, 'K-방산 도시 추진단' 구성</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
+          <t>http://www.newstnt.com/news/articleView.html?idxno=605880</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
+          <t>Thu, 09 Apr 2026 11:42:00 +0900</t>
         </is>
       </c>
       <c r="E164">
-        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg", IMAGE("https://cdn.newstnt.com/news/photo/202604/605880_634006_3841.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4377,21 +4376,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
+          <t>이돈승 '방산-수소' 전문가 영입··· 완주산업 재편</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
+          <t>http://www.jjn.co.kr/news/articleView.html?idxno=1037411</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
+          <t>Tue, 07 Apr 2026 19:46:00 +0900</t>
         </is>
       </c>
       <c r="E165">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg", IMAGE("https://cdn.jjn.co.kr/news/thumbnail/202604/1037411_263083_1916_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4401,21 +4400,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
+          <t>이돈승 “수소·방산으로 완주 산업 재편”…실행 조직 구상 제시</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002435956?sid=102</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
+          <t>Tue, 07 Apr 2026 16:13:00 +0900</t>
         </is>
       </c>
       <c r="E166">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/04/07/0002435956_001_20260407161309436.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4425,21 +4424,21 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
+          <t>이돈승 예비후보, 완주 성장 이끌 방산·수소전문가 영입</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/031/0001020297?sid=102</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 15:53:00 +0900</t>
         </is>
       </c>
       <c r="E167">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/031/2026/04/07/0001020297_001_20260407155307222.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4449,21 +4448,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
+          <t>&amp;quot;야당 첩자&amp;quot; 소리 들으며 방사청 지켜낸 사람들…K방산 수출 신화의 뒷...</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000924040?sid=100</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 07 Apr 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E168">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/04/07/0000924040_001_20260407140121172.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4473,21 +4472,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
+          <t>&amp;quot;2억5천만→10억 달러&amp;quot;…방사청 출범 2년 만에 방산수출 4배 뛴 까닭은</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000921315?sid=100</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
+          <t>Tue, 24 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E169">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/24/0000921315_001_20260325132017191.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4497,21 +4496,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
+          <t>방산비리 척결하려 만든 조직이 'K-방산' 신화 썼다…방위사업청 탄생 ...</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000918578?sid=100</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
+          <t>Tue, 10 Mar 2026 14:01:00 +0900</t>
         </is>
       </c>
       <c r="E170">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/03/10/0000918578_001_20260310140116810.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4521,21 +4520,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>전북대, 방산 인공지능 인재양성 선정</t>
+          <t>[창간 11주년 특별기획-조선·방산산업 전망] ③ K-방산, 글로벌 시장 주...</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=822262</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
+          <t>Mon, 09 Mar 2026 07:00:00 +0900</t>
         </is>
       </c>
       <c r="E171">
-        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202603/822262_827126_813_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4545,21 +4544,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
+          <t>전북대, 방산 인공지능 인재양성 선정</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
+          <t>https://www.naeil.com/news/read/580357?ref=naver</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
+          <t>Sun, 08 Mar 2026 17:46:00 +0900</t>
         </is>
       </c>
       <c r="E172">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://static.naeil.com/img/rect_logo.jpg", IMAGE("https://static.naeil.com/img/rect_logo.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4569,21 +4568,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
+          <t>전북대, 첨단인재양성 부트캠프 사업 선정</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003507025?sid=102</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
+          <t>Thu, 05 Mar 2026 14:49:00 +0900</t>
         </is>
       </c>
       <c r="E173">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/03/05/0003507025_001_20260305145014307.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4593,21 +4592,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
+          <t>정체기 맞은 K-방산, 향후 대형 수주로 반등 노린다</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1405767</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
+          <t>Tue, 25 Aug 2026 15:36:00 +0900</t>
         </is>
       </c>
       <c r="E174">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1405767_1193937_3424_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4617,21 +4616,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
+          <t>K9 미국에 첫 수출…한화, 10조까지 넘본다</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545459?sid=101</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
+          <t>Thu, 20 Aug 2026 00:02:00 +0900</t>
         </is>
       </c>
       <c r="E175">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/20/0003545459_001_20260820000423486.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4641,21 +4640,21 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
+          <t>‘분당 9발’로 미국 사로잡은 K9 자주포</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/449/0000357459?sid=100</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
+          <t>Wed, 19 Aug 2026 19:53:00 +0900</t>
         </is>
       </c>
       <c r="E176">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800", IMAGE("https://imgnews.pstatic.net/image/449/2026/08/19/0000357459_001_20260819200539091.jpeg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4665,21 +4664,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
+          <t>K방산 미국 시장 뚫었다…한화 K9, 美육군 차세대 자주포 계약</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003545338?sid=101</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
+          <t>Wed, 19 Aug 2026 14:50:00 +0900</t>
         </is>
       </c>
       <c r="E177">
-        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/025/2026/08/19/0003545338_001_20260819172814875.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4689,21 +4688,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
+          <t>필리조선소 다음은 오스탈…한화, 美 군함시장 정조준</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
+          <t>https://www.newsway.co.kr/news/view?ud=2026081213102422886</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
+          <t>Wed, 12 Aug 2026 13:32:00 +0900</t>
         </is>
       </c>
       <c r="E178">
-        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
+        <f>HYPERLINK("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg", IMAGE("https://nimage.newsway.co.kr/photo/2026/01/09/20260109000008_1200.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4713,21 +4712,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
+          <t>K-방산의 아픈 손 KAI…'공공 틀' 갇혀 자생력 한계</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4429567</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
+          <t>Tue, 11 Aug 2026 13:12:00 +0900</t>
         </is>
       </c>
       <c r="E179">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg", IMAGE("https://cdn.news.einfomax.co.kr/news/thumbnail/202608/4429567_336147_562_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4737,21 +4736,21 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
+          <t>[기획]&amp;quot;가성비만으론 한계&amp;quot;…K-방산, 성장 전략 다시 짜야</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1400586</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
+          <t>Mon, 10 Aug 2026 15:30:00 +0900</t>
         </is>
       </c>
       <c r="E180">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202608/1400586_1188464_1020_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4761,21 +4760,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
+          <t>1800문 깔린 한화 K-9, 애프터마켓도 커진다</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1397184</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:12:00 +0900</t>
         </is>
       </c>
       <c r="E181">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1397184_1185010_558_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4785,21 +4784,21 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
+          <t>“한일, 해양수송로 공유… 분쟁시 운명공동체 될 것”</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003737284?sid=104</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
+          <t>Wed, 29 Jul 2026 04:36:00 +0900</t>
         </is>
       </c>
       <c r="E182">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/29/0003737284_001_20260729104016198.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4809,21 +4808,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
+          <t>[기획]북미서 고배 마셨지만…HD현대·한화, 남미 함정 수요 정조준</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2605457</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1395625</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
+          <t>Mon, 27 Jul 2026 15:38:00 +0900</t>
         </is>
       </c>
       <c r="E183">
-        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1395625_1183389_4926_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4833,21 +4832,21 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
+          <t>포티투마루, ‘K-팔란티어’ 육성 위한 ‘국방 AI 생태계’ 전략 제시</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
+          <t>https://www.etoday.co.kr/news/view/2605457</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
+          <t>Tue, 21 Jul 2026 08:32:00 +0900</t>
         </is>
       </c>
       <c r="E184">
-        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
+        <f>HYPERLINK("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png", IMAGE("https://img.etoday.co.kr/pto_db/2026/07/20260721082646_2361751_1000_276.png"))</f>
         <v/>
       </c>
     </row>
@@ -4857,21 +4856,21 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
+          <t>[기획]中 &amp;quot;美 대신 우리와&amp;quot;…K-조선, 글로벌 해양 안보 핵심축 부상</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
+          <t>https://www.m-i.kr/news/articleView.html?idxno=1392350</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
+          <t>Sun, 19 Jul 2026 13:00:00 +0900</t>
         </is>
       </c>
       <c r="E185">
-        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
+        <f>HYPERLINK("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg", IMAGE("https://cdn.m-i.kr/news/thumbnail/202607/1392350_1180000_1950_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4881,21 +4880,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
+          <t>KAI 인수 침 바르는 한화, 걸림돌 뭐가 있을까 [이슈체크]</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
+          <t>https://news.mtn.co.kr/news-detail/2026071509051891124</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
+          <t>Thu, 16 Jul 2026 09:40:00 +0900</t>
         </is>
       </c>
       <c r="E186">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg", IMAGE("https://assets.mtn.co.kr/mtn/2026/07/CvTDLi9bAegIuKEQ/image/20260716_173357//04dfad236211158be9f086426cf71de5fd49ab083140ddee4a7495c31d997fd9.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4905,21 +4904,21 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
+          <t>잇단 수출 실패... 한국 잠수함 생태계 '일감 절벽' 경고등</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942297?sid=101</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
+          <t>Wed, 15 Jul 2026 04:30:00 +0900</t>
         </is>
       </c>
       <c r="E187">
-        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/469/2026/07/15/0000942297_001_20260715061440510.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4929,21 +4928,21 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
+          <t>[이슈체크]한화, KAI 인수...K-방산 판도 변화</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
+          <t>http://www.hansbiz.co.kr/news/articleView.html?idxno=849986</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
+          <t>Mon, 13 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E188">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg", IMAGE("https://cdn.hansbiz.co.kr/news/thumbnail/202607/849986_866987_384_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -4953,21 +4952,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
+          <t>캐나다서 고배 마신 한화오션, 미국선 러브콜…'전투함 건조' 길 열릴까...</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/277/0005787343?sid=101</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
+          <t>Wed, 08 Jul 2026 16:32:00 +0900</t>
         </is>
       </c>
       <c r="E189">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/277/2026/07/08/0005787343_001_20260709105112709.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -4977,21 +4976,21 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
+          <t>“가성비만으론 나토 ‘방산 블록’ 못 뚫어… 안보 협력 강화부터”</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003986369?sid=101</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:52:00 +0900</t>
         </is>
       </c>
       <c r="E190">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/023/2026/07/08/0003986369_001_20260708103425084.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -5001,21 +5000,21 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>성능보다 우선한 '동맹'…캐나다, 왜 독일 선택했나?</t>
+          <t>K방산, 강호 獨 맞서며 경쟁력 확인… 중동·동남아 기회 남았다</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/448/0000625036?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/005/0001859579?sid=101</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Tue, 07 Jul 2026 21:20:00 +0900</t>
+          <t>Wed, 08 Jul 2026 00:13:00 +0900</t>
         </is>
       </c>
       <c r="E191">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/448/2026/07/07/2026070790293_thumb_092435_20260707212614334.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/005/2026/07/08/2026070719160649371_1783419366_1783416634_20260708001316680.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260923032514", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260923032514"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260924034428", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260924034428"))</f>
         <v/>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260923032627", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260923032627"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260924034539", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260924034539"))</f>
         <v/>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260923032642", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260923032642"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260924034553", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260924034553"))</f>
         <v/>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260923032712", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260923032712"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260924034624", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260924034624"))</f>
         <v/>
       </c>
     </row>
@@ -2911,12 +2911,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
+          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="E104">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -2935,12 +2935,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>전북대, AI-무인전투 이끌 ‘K-방산 인재’ 650명 키운다</t>
+          <t>“한국의 방산 4대 강국 도약에 기여하겠다”</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003736186?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003736187?sid=102</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="E105">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736186_001_20260724091109852.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/020/2026/07/24/0003736187_001_20260724091209601.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260923032750", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260923032750"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260924034701", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260924034701"))</f>
         <v/>
       </c>
     </row>

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="E64">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260924034428", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260924034428"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260925034549", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/17/.cache/512/20260817500416.jpg?v=20260925034549"))</f>
         <v/>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="E87">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260924034539", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260924034539"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260925034709", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/19/.cache/512/20260819500011.png?v=20260925034709"))</f>
         <v/>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="E91">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260924034553", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260924034553"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260925034723", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/08/12/20260812500674.webp?v=20260925034723"))</f>
         <v/>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="E103">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260924034624", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260924034624"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260925034756", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/26/.cache/512/20260726500497.jpg?v=20260925034756"))</f>
         <v/>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="E120">
-        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260924034701", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260924034701"))</f>
+        <f>HYPERLINK("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260925034839", IMAGE("https://stqnq5ux4599.edge.naverncp.com/data2//content/image/2026/07/12/.cache/512/20260712500405.jpg?v=20260925034839"))</f>
         <v/>
       </c>
     </row>
@@ -3332,10 +3332,9 @@
           <t>Thu, 09 Jul 2026 17:44:00 +0900</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>이미지 없음</t>
-        </is>
+      <c r="E121">
+        <f>HYPERLINK("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg", IMAGE("https://img.asiatoday.co.kr/file/2026y/07m/10d/2026071001000693700037121.jpg"))</f>
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -4269,9 +4268,10 @@
           <t>Sun, 12 Apr 2026 16:32:00 +0900</t>
         </is>
       </c>
-      <c r="E160">
-        <f>HYPERLINK("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg", IMAGE("//kookbang.dema.mil.kr/newspaper/2022/images/common/meta_logo.jpg"))</f>
-        <v/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>이미지 없음</t>
+        </is>
       </c>
     </row>
     <row r="161">

--- a/언론보도_기고칼럼_db.xlsx
+++ b/언론보도_기고칼럼_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,21 +462,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>** 전북대, 15곳 방산기업과 ‘교육부터 채용까지' 연계</t>
+          <t>** 전북대학교, 방산기업 15곳과 손잡고 '교육부터 채용까지' 인재양성 본...</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=888194</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=211113</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sun, 20 Sep 2026 18:24:00 +0900</t>
+          <t>Fri, 25 Sep 2026 06:34:00 +0900</t>
         </is>
       </c>
       <c r="E2">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_888194_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_888194_202609_0.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202609/211113_480747_3318_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202609/211113_480747_3318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -486,21 +486,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>** 전북대, 방산기업 15곳과 '교육부터 채용까지'</t>
+          <t>** 전북대, 15곳 방산기업과 ‘교육부터 채용까지' 연계</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004191066?sid=102</t>
+          <t>https://sjbnews.com/news/news.php?number=888194</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fri, 18 Sep 2026 16:55:00 +0900</t>
+          <t>Sun, 20 Sep 2026 18:24:00 +0900</t>
         </is>
       </c>
       <c r="E3">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/079/2026/09/18/0004191066_001_20260918165510107.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/079/2026/09/18/0004191066_001_20260918165510107.jpg?type=w800"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_888194_202609_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_888194_202609_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -534,21 +534,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>** 전북대, 방산기업 15곳과 '인재 육성 채용연계 산학협력 모델' 본격 가동</t>
+          <t>** 전북대, 방산기업 15곳과 '교육부터 채용까지' 잇는다</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003468198?sid=102</t>
+          <t>https://news.unn.net/news/articleView.html?idxno=597714</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 18 Sep 2026 10:49:00 +0900</t>
+          <t>Fri, 18 Sep 2026 11:00:00 +0900</t>
         </is>
       </c>
       <c r="E5">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/18/0003468198_001_20260918104913691.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/18/0003468198_001_20260918104913691.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.news.unn.net/news/thumbnail/202609/597714_423650_5744_v150.jpg", IMAGE("https://cdn.news.unn.net/news/thumbnail/202609/597714_423650_5744_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -558,21 +558,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>** 전북대학교 계약정원제 사업, 우주항공·AI·첨단방산 미래인재 양성 '비...</t>
+          <t>** 전북대, 방산기업 15곳과 '인재 육성 채용연계 산학협력 모델' 본격 가동</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.lecturernews.com/news/articleView.html?idxno=210469</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003468198?sid=102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sat, 12 Sep 2026 16:34:00 +0900</t>
+          <t>Fri, 18 Sep 2026 10:49:00 +0900</t>
         </is>
       </c>
       <c r="E6">
-        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/09/18/0003468198_001_20260918104913691.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/09/18/0003468198_001_20260918104913691.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -582,21 +582,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
+          <t>** 전북대학교 계약정원제 사업, 우주항공·AI·첨단방산 미래인재 양성 '비...</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://sjbnews.com/news/news.php?number=884391</t>
+          <t>https://www.lecturernews.com/news/articleView.html?idxno=210469</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
+          <t>Sat, 12 Sep 2026 16:34:00 +0900</t>
         </is>
       </c>
       <c r="E7">
-        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
+        <f>HYPERLINK("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg", IMAGE("https://cdn.lecturernews.com/news/thumbnail/202609/210469_479890_445_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -606,21 +606,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
+          <t>** 전북대, 전북 최초 국방사업관리사 재직자 전문과정</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
+          <t>https://sjbnews.com/news/news.php?number=884391</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
+          <t>Mon, 03 Aug 2026 18:52:00 +0900</t>
         </is>
       </c>
       <c r="E8">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
+        <f>HYPERLINK("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg", IMAGE("http://sjbnews.com/data/data_file/thum_884391_202608_0.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -630,21 +630,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
+          <t>** 전북 첫 '국방사업관리사' 재직자 과정 운영…전북대, 전문인력 45명 배...</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002450696?sid=102</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
+          <t>Mon, 03 Aug 2026 12:51:00 +0900</t>
         </is>
       </c>
       <c r="E9">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/08/03/0002450696_001_20260803125110937.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -654,21 +654,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
+          <t>** 전북대, 국방사업관리사 재직자 전문과정 마쳐…&amp;quot;45명 수료&amp;quot;</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014104540?sid=102</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
+          <t>Mon, 03 Aug 2026 11:26:00 +0900</t>
         </is>
       </c>
       <c r="E10">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/03/NISI20260803_0002202803_web_20260803112403_20260803112716009.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -678,21 +678,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
+          <t>** 전북대, 방산혁신클러스터 전문인력 양성 첫 발…'국방사업관리사 재직...</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/030/0003453553?sid=102</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
+          <t>Mon, 03 Aug 2026 10:32:00 +0900</t>
         </is>
       </c>
       <c r="E11">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/030/2026/08/03/0003453553_001_20260803103216594.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -702,21 +702,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
+          <t>** [전북24시]전북대, 방산인재양성 국내외 전문가 3명 교수 초빙</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
+          <t>https://n.news.naver.com/mnews/article/586/0000134883?sid=102</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:50:00 +0900</t>
         </is>
       </c>
       <c r="E12">
-        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800", IMAGE("https://imgnews.pstatic.net/image/586/2026/07/30/0000134883_001_20260730165012665.png?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -726,21 +726,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
+          <t>** 전북대, 국내외 대표 방산기업 임원 3명 객원교수 초빙</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
+          <t>http://www.jeollailbo.com/news/articleView.html?idxno=806831</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
+          <t>Thu, 30 Jul 2026 16:42:00 +0900</t>
         </is>
       </c>
       <c r="E13">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg", IMAGE("https://cdn.jeollailbo.com/news/thumbnail/202607/806831_194490_400_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -750,21 +750,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
+          <t>** 전북대 방산기업 임원 3명 객원교수로 초빙.. 현장형 인재양성 본격화</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621484</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
+          <t>Thu, 30 Jul 2026 10:30:00 +0900</t>
         </is>
       </c>
       <c r="E14">
-        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621484_534541_2823_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -774,21 +774,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
+          <t>** 모레, 전북대서 피지컬 AI 기술이전…&amp;quot;국방·공공안전 AI 플랫폼 개발&amp;quot;</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
+          <t>https://www.irobotnews.com/news/articleView.html?idxno=47665</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
+          <t>Wed, 29 Jul 2026 15:56:00 +0900</t>
         </is>
       </c>
       <c r="E15">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg", IMAGE("https://cdn.irobotnews.com/news/photo/202607/47665_102259_5229.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -798,21 +798,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
+          <t>** 전북대 조형기 교수팀 피지컬AI 원천기술 모레에 기술이전.. '국방/공공...</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=621384</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:30:00 +0900</t>
         </is>
       </c>
       <c r="E16">
-        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202607/621384_534434_2858_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -822,21 +822,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
+          <t>** 모레, 전북대와 피지컬 AI 핵심기술 이전 계약 체결…국방·공공안전 AI...</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
+          <t>https://www.epnc.co.kr/news/articleView.html?idxno=404883</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
+          <t>Wed, 29 Jul 2026 12:10:00 +0900</t>
         </is>
       </c>
       <c r="E17">
-        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
+        <f>HYPERLINK("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg", IMAGE("https://cdn.epnc.co.kr/news/photo/202607/404883_405216_476.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -846,21 +846,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
+          <t>** 전북대 첨단방위산업학과 서유정 학생.. 탈레스코리아 'STEM for ALL' 장학...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
+          <t>https://www.veritas-a.com/news/articleView.html?idxno=623466</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
+          <t>Tue, 18 Aug 2026 12:24:00 +0900</t>
         </is>
       </c>
       <c r="E18">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg", IMAGE("https://cdn.veritas-a.com/news/thumbnail/202608/623466_536560_2318_v150.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -870,21 +870,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>** 전북대, 한화·현대로템·보잉 등 임원 객원교수 초빙…방산 인재양성 ...</t>
+          <t>** 전북대, 글로벌 항공·방위기업 '탈레스코리아' 장학생 배출</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.betanews.net/article/view/beta202607300039</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014132599?sid=102</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:10:00 +0900</t>
+          <t>Tue, 18 Aug 2026 11:30:00 +0900</t>
         </is>
       </c>
       <c r="E19">
-        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/08/18/NISI20260818_0002214747_web_20260818112657_20260818113120970.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -894,21 +894,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>美 지상·해양 방산사업 핵심축 '한화디펜스USA'…현지화 속도</t>
+          <t>** 전북대, 한화·현대로템·보잉 등 임원 객원교수 초빙…방산 인재양성 ...</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://news.mtn.co.kr/news-detail/2026092216533024563</t>
+          <t>https://www.betanews.net/article/view/beta202607300039</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 22 Sep 2026 17:50:00 +0900</t>
+          <t>Thu, 30 Jul 2026 14:10:00 +0900</t>
         </is>
       </c>
       <c r="E20">
-        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/09/22/2026092216533024563_00_228.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/09/22/2026092216533024563_00_228.jpg"))</f>
+        <f>HYPERLINK("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg", IMAGE("https://www.betanews.net/data/beta/image/2026/07/30/beta20260730000040.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -918,21 +918,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>전북대, 방산기업 15곳과 맞춤형 인재양성 프로그램 운영</t>
+          <t>생산부터 정비까지…K-방산, 전장 밖으로 넓어지는 AX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014200391?sid=102</t>
+          <t>https://www.g-enews.com/view.php?ud=202609231520348026ea14faf6f5_1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 18 Sep 2026 16:41:00 +0900</t>
+          <t>Fri, 25 Sep 2026 09:02:00 +0900</t>
         </is>
       </c>
       <c r="E21">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026092315142705424ea14faf6f5175197343.jpg", IMAGE("https://nimage.g-enews.com/phpwas/restmb_allidxmake.php?idx=5&amp;simg=2026092315142705424ea14faf6f5175197343.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -942,21 +942,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>첨단 드론 잇단 추락…방산 ‘무인 경쟁력’ 우려 확대</t>
+          <t>美 지상·해양 방산사업 핵심축 '한화디펜스USA'…현지화 속도</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>http://www.newstomato.com/ReadNews.aspx?no=1314054&amp;inflow=N</t>
+          <t>https://news.mtn.co.kr/news-detail/2026092216533024563</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 15:00:00 +0900</t>
+          <t>Tue, 22 Sep 2026 17:50:00 +0900</t>
         </is>
       </c>
       <c r="E22">
-        <f>HYPERLINK("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945", IMAGE("https://image.newstomato.com/newsimg/2026/9/17/1314054/attach.jpg?v=202609180945"))</f>
+        <f>HYPERLINK("https://menu.mtn.co.kr/upload/article/2026/09/22/2026092216533024563_00_228.jpg", IMAGE("https://menu.mtn.co.kr/upload/article/2026/09/22/2026092216533024563_00_228.jpg"))</f>
         <v/>
       </c>
     </row>
@@ -966,21 +966,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>&amp;quot;민주당 맹목적 지지 벗어나 전북발전 성과 요구하자&amp;quot;…오창환 전북대 ...</t>
+          <t>전북대, 방산기업 15곳과 맞춤형 인재양성 프로그램 운영</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002457143?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014200391?sid=102</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 11:00:00 +0900</t>
+          <t>Fri, 18 Sep 2026 16:41:00 +0900</t>
         </is>
       </c>
       <c r="E23">
-        <f>HYPERLINK("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/002/2026/09/17/0002457143_001_20260917110009733.jpg?type=w800"))</f>
+        <f>HYPERLINK("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800", IMAGE("https://imgnews.pstatic.net/image/003/2026/09/18/NISI20260918_0002243729_web_20260918163923_20260918164224349.jpg?type=w800"))</f>
         <v/>
       </c>
     </row>
@@ -990,21 +990,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>K방산, 100조 수주에도 점유율 2%…&amp;quot;체급 키워 메인 시장 가야&amp;quot;</t>
+          <t>첨단 드론 잇단 추락…방산 ‘무인 경쟁력’ 우려 확대</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.insightkorea.co.kr/news/articleView.html?idxno=254595</t>
+          <t>http://www.newstomato.com/ReadNews.aspx?no=1314054&amp;inflow=N</t>
         </is>
  